--- a/doc/POPPy.xlsx
+++ b/doc/POPPy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oreil\Documents\GitHub\poppy\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D97764B2-E32F-446D-90E0-29863DB1F28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59889556-175D-48ED-9403-C538195FE684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="313">
   <si>
     <t>Database</t>
   </si>
@@ -59,9 +60,6 @@
     <t>Lisence</t>
   </si>
   <si>
-    <t>Location</t>
-  </si>
-  <si>
     <t>Available File Formats</t>
   </si>
   <si>
@@ -74,9 +72,6 @@
     <t>Compounds</t>
   </si>
   <si>
-    <t>Names</t>
-  </si>
-  <si>
     <t xml:space="preserve">Disease </t>
   </si>
   <si>
@@ -104,9 +99,6 @@
     <t>MIT license, CC0 license</t>
   </si>
   <si>
-    <t>Zendo</t>
-  </si>
-  <si>
     <t>Postgres Database Dump, CSV Format File, SDF Format, Collection Specific Downloads</t>
   </si>
   <si>
@@ -233,9 +225,6 @@
     <t xml:space="preserve">Ceative Commons Attribution Lisence </t>
   </si>
   <si>
-    <t xml:space="preserve">Downloadable dataset, suplementary data table </t>
-  </si>
-  <si>
     <t>Yes, 1127-medicinal plants</t>
   </si>
   <si>
@@ -287,9 +276,6 @@
     <t xml:space="preserve">Free use but can not be altered and subsequently redistributed under the origional name and must be acknowledged </t>
   </si>
   <si>
-    <t>GitHub</t>
-  </si>
-  <si>
     <t>GirHub available to collaborate on/change, each ontology has its own links to download data</t>
   </si>
   <si>
@@ -360,9 +346,6 @@
   </si>
   <si>
     <t>Collective Molecular Activities of Useful Plants (CMAUP)</t>
-  </si>
-  <si>
-    <t>This is the given link but I am unable to open it: http://bidd2.nus.edu.sg/CMAUP/</t>
   </si>
   <si>
     <t>Xian Zeng, Peng Zhang, Yali Wang, Chu Qin, Shangying Chen, Weidong He, Lin Tao, Ying Tan, Dan Gao, Bohua Wang, Zhe Chen, Weiping Chen, Yu Yang Jiang, Yu Zong Chen, CMAUP: a database of collective molecular activities of useful plants, Nucleic Acids Research, Volume 47, Issue D1, 08 January 2019, Pages D1118–D1127, https://doi.org/10.1093/nar/gky965</t>
@@ -606,9 +589,6 @@
     <t>Journal of Plant Pathology</t>
   </si>
   <si>
-    <t>JSTOR</t>
-  </si>
-  <si>
     <t>Worldwide- each plant specifies origin</t>
   </si>
   <si>
@@ -853,9 +833,6 @@
   </si>
   <si>
     <t>Medicinal Plants in the Republic of Korea</t>
-  </si>
-  <si>
-    <t>https://www.who.int/publications/i/item/9290611200</t>
   </si>
   <si>
     <t>© World Health Organization 1998</t>
@@ -1147,12 +1124,167 @@
       <t>. World Health Organization, Regional Office for the Western Pacific.</t>
     </r>
   </si>
+  <si>
+    <t>Handbook of Ayurvedic Medicinal Plants</t>
+  </si>
+  <si>
+    <t>First pulished by CRC Press LLC © 1990  © 2001 by CRC Press LLC</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (latin name, family, vernacular names, habitat, morphological characteristics, parts used, aturvedic description, action and uses, chemical constituents, pharmalogical action, medicinal properties and uses, doses)</t>
+  </si>
+  <si>
+    <t>Kapoor, L.D. (2001). Handbook of Ayurvedic Medicinal Plants: Herbal Reference Library (1st ed.). Routledge. https://doi.org/10.1201/9780203719473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicinal Plants in the South Pacific </t>
+  </si>
+  <si>
+    <t>World Health Organization. Regional Office for the Western Pacific (1998). Medicinal plants in the South Pacific : information on 102 commonly used medicinal plants in the South Pacific. WHO Regional Office for the Western Pacific. http://iris.wpro.who.int/handle/10665.1/6738</t>
+  </si>
+  <si>
+    <t>ISBN 92 9061 1189 © WorldHeallbOrganizalion 1998</t>
+  </si>
+  <si>
+    <t>Kinda- gives constituetns and biological activity of each plant</t>
+  </si>
+  <si>
+    <t>Kinda- gives the chemical constituents</t>
+  </si>
+  <si>
+    <t>Kinda- sometimes mentioned in medicinal properties and uses</t>
+  </si>
+  <si>
+    <t>Kinda- mentioned sometimes in traditional uses</t>
+  </si>
+  <si>
+    <t>South Pacific</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (latin name, local names, description, habitat, distribution, constituents, biological activity, traditional uses)</t>
+  </si>
+  <si>
+    <t>The Tropical Plant Database</t>
+  </si>
+  <si>
+    <t>© Copyrighted 2019 Rain-Tree Publishers All rights reserved.</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (family, genus, species, synonyms, common names, parts used, properties and actions, tribal and herbal medicine uses, plant chemicals, biological activities and clinical research, current practical uses, plant summary, worldwide ethnomedical uses, published research)</t>
+  </si>
+  <si>
+    <t>Wealth of the Rainforest, Pharmacy to the World, by Leslie Taylor, Copyrighted 1996 to present by Leslie Taylor, Milam County, Texas 77857. Online at http://www.rain-tree.com</t>
+  </si>
+  <si>
+    <t>You have to get written authorization from the author to use, transmit, or reproduce the database (There is educational exceptions but I'm not sure if this would count)</t>
+  </si>
+  <si>
+    <t>https://www.stuartxchange.org/CompleteList.html</t>
+  </si>
+  <si>
+    <r>
+      <t>© All content, imagery, and photos are copyrighted / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Godofredo U. Stuart, Jr., MD</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t> • </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="7"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>StuartXchange</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippine Medicinal Plants </t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Data Format</t>
+  </si>
+  <si>
+    <t>Still Available?</t>
+  </si>
+  <si>
+    <t>PubMed ID</t>
+  </si>
+  <si>
+    <t>Identifiers</t>
+  </si>
+  <si>
+    <t>Phytochemical- general</t>
+  </si>
+  <si>
+    <t>Biomedical- general</t>
+  </si>
+  <si>
+    <t>Online Database</t>
+  </si>
+  <si>
+    <t>No PubMed article</t>
+  </si>
+  <si>
+    <t>Plant taxonomy- medicinal</t>
+  </si>
+  <si>
+    <t>Plant taxonomy- general</t>
+  </si>
+  <si>
+    <t>http://bidd2.nus.edu.sg/CMAUP/</t>
+  </si>
+  <si>
+    <t>Journal Article</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.who.int/publications/i/item/9290611200 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://files.spiritmaji.com/books/diet-herbal-ayurveda-remedies/Handbook%20of%20Ayurvedic%20Medicinal%20-%20L.D.%20Kapoor.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://iris.who.int/items/a381e797-ac83-4601-a845-45890ef76413 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rain-tree.com/plants.htm </t>
+  </si>
+  <si>
+    <t>Downloadable dataset, suplementary data table (apparently)</t>
+  </si>
+  <si>
+    <t>Downloadable links to pages with text of code information, downloads as H5 files</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1265,6 +1397,33 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF212121"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1321,7 +1480,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1374,6 +1533,14 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1710,1421 +1877,2049 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:S37"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="32.26953125" style="7" customWidth="1"/>
-    <col min="4" max="6" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.81640625" style="7" customWidth="1"/>
-    <col min="8" max="9" width="21.7265625" style="7" customWidth="1"/>
-    <col min="10" max="12" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="22.7265625" style="7" customWidth="1"/>
-    <col min="14" max="14" width="34.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.1796875" style="7"/>
+    <col min="1" max="1" width="9.1796875" style="7"/>
+    <col min="2" max="2" width="14.7265625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.54296875" style="7" customWidth="1"/>
+    <col min="5" max="8" width="32.26953125" style="7" customWidth="1"/>
+    <col min="9" max="11" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="21.7265625" style="7" customWidth="1"/>
+    <col min="14" max="16" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.7265625" style="7" customWidth="1"/>
+    <col min="18" max="18" width="34.1796875" style="7" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.1796875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:19" ht="168" x14ac:dyDescent="0.3">
+      <c r="A2" s="7">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="D2" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>14</v>
       </c>
+      <c r="F2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="25">
+        <v>39588778</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S2" s="7">
+        <v>2026</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" ht="168" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+    <row r="3" spans="1:19" ht="154" x14ac:dyDescent="0.3">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="25">
+        <v>17932057</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S3" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="210" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="25">
+        <v>39558177</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="168" x14ac:dyDescent="0.3">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" s="25">
+        <v>14681407</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S5" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="126" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="S6" s="7">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="182" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="25">
+        <v>32761142</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q7" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S7" s="7">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="H8" s="25">
+        <v>17989687</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="R8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S8" s="7">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="25">
+        <v>39552041</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S9" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="238" x14ac:dyDescent="0.3">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="25">
+        <v>32117874</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="R10" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S10" s="7">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="154.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>305</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="25">
+        <v>30357356</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="140" x14ac:dyDescent="0.3">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="6">
+        <v>35616633</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S12" s="7">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="168" x14ac:dyDescent="0.3">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="H13" s="25">
+        <v>41243954</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q13" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="R13" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="93.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="126" x14ac:dyDescent="0.3">
+      <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B16" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="H16" s="25">
+        <v>24735618</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="S16" s="7">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="126" x14ac:dyDescent="0.3">
+      <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B17" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>267</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="H17" s="25">
+        <v>36910986</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q17" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" ht="126" x14ac:dyDescent="0.3">
+      <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B18" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H18" s="25">
+        <v>39558165</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q18" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" ht="140" x14ac:dyDescent="0.3">
+      <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="B19" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="H19" s="25">
+        <v>41217946</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S19" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" ht="112" x14ac:dyDescent="0.3">
+      <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="B20" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R20" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="98" x14ac:dyDescent="0.3">
+      <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="B21" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="S21" s="7">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="70" x14ac:dyDescent="0.3">
+      <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="B22" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E22" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P22" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="S22" s="7">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="70" x14ac:dyDescent="0.3">
+      <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="B23" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R23" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="S23" s="7">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" ht="70" x14ac:dyDescent="0.3">
+      <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="B24" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O24" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="P24" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R24" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" ht="98" x14ac:dyDescent="0.3">
+      <c r="A25" s="7">
+        <v>24</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>306</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P25" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q25" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="R25" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A26" s="7">
         <v>25</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="B26" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="R26" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="S26" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="56" x14ac:dyDescent="0.3">
+      <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="B27" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O27" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="R27" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="S27" s="7">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="B28" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="O28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P28" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="S28" s="7">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="56" x14ac:dyDescent="0.3">
+      <c r="A29" s="7">
         <v>28</v>
       </c>
-      <c r="O2" s="7">
+      <c r="B29" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O29" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="R29" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="S29" s="7">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="84" x14ac:dyDescent="0.3">
+      <c r="A30" s="7">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="P30" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="R30" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="S30" s="7">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="56" x14ac:dyDescent="0.3">
+      <c r="A31" s="7">
+        <v>30</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="K31" s="19" t="s">
+        <v>260</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="O31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S31" s="7">
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="154" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="5" t="s">
+    <row r="32" spans="1:19" ht="98.5" x14ac:dyDescent="0.35">
+      <c r="A32" s="7">
         <v>31</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="B32" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>307</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="I32" s="22" t="s">
+        <v>270</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P32" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q32" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R32" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="S32" s="7">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A33" s="7">
         <v>32</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="B33" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>308</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>275</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O33" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="P33" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q33" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="R33" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="S33" s="7">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="126.5" x14ac:dyDescent="0.35">
+      <c r="A34" s="7">
+        <v>33</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="P34" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q34" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="R34" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="S34" s="7">
+        <v>1998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="112.5" x14ac:dyDescent="0.35">
+      <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="B35" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P35" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="S35" s="7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="7">
         <v>35</v>
       </c>
-      <c r="I3" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O3" s="7">
-        <v>2026</v>
+      <c r="C36" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="K36" s="24" t="s">
+        <v>291</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="210" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" ht="168" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O5" s="7">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="126" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="O6" s="7">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="182" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="7">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="84" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O8" s="7">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="84" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O9" s="7">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="238" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O10" s="7">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="154" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="140" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="K12" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="M12" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O12" s="7">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="168" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="93.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="126" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="M16" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="O16" s="7">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" ht="126" x14ac:dyDescent="0.3">
-      <c r="A17" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C17" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="M17" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" ht="126" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" ht="140" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>177</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="M19" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O19" s="7">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="112" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="98" x14ac:dyDescent="0.3">
-      <c r="A21" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B21" s="15" t="s">
-        <v>191</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="E21" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M21" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="O21" s="7">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" ht="70" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="F22" s="16" t="s">
-        <v>199</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N22" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="O22" s="7">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="70" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="B23" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E23" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="F23" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="O23" s="7">
-        <v>1970</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="70" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>210</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="F24" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="98" x14ac:dyDescent="0.3">
-      <c r="A25" s="17" t="s">
-        <v>213</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M25" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" ht="84" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="O26" s="7">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" ht="56" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="B27" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>233</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="M27" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="N27" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="O27" s="7">
-        <v>1989</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" ht="84" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M28" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="O28" s="7">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" ht="56" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="M29" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="O29" s="7">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="84" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="O30" s="7">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="56" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="O31" s="7">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="98" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>278</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="N32" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="O32" s="7">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="37" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E37" s="21"/>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="J37" s="21"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{EC3B56C5-8274-496C-BB46-8310F6EB00B5}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{848D4D3B-8E32-495F-B01F-49C5B717982E}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{9873785C-418F-4EA0-838A-0A12B2DBA581}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{FD7B7A15-A769-4289-AF7B-4C9C97DEFC90}"/>
-    <hyperlink ref="C2" r:id="rId5" display="Venkata Chandrasekhar, Kohulan Rajan, Sri Ram Sagar Kanakam, Nisha Sharma, Viktor Weißenborn, Jonas Schaub, Christoph Steinbeck, COCONUT 2.0: a comprehensive overhaul and curation of the collection of open natural products database, Nucleic Acids Research, Volume 53, Issue D1, 6 January 2025, Pages D634–D643, https://doi.org/10.1093/nar/gkae1063" xr:uid="{C1A87BBC-6280-4F1D-8AE2-9ED78A4E86E4}"/>
-    <hyperlink ref="C3" r:id="rId6" display="Kirill Degtyarenko, Paula de Matos, Marcus Ennis, Janna Hastings, Martin Zbinden, Alan McNaught, Rafael Alcántara, Michael Darsow, Mickaël Guedj, Michael Ashburner, ChEBI: a database and ontology for chemical entities of biological interest, Nucleic Acids Research, Volume 36, Issue suppl_1, 1 January 2008, Pages D344–D350, https://doi.org/10.1093/nar/gkm791" xr:uid="{62CD6EEC-6607-4050-904C-77E7C59253BE}"/>
-    <hyperlink ref="C4" r:id="rId7" display="Kai Gao, Liu Liu, Shuangshuang Lei, Zhinong Li, Peipei Huo, Zhihao Wang, Lei Dong, Wenxin Deng, Dechao Bu, Xiaoxi Zeng, Chun Li, Yi Zhao, Wei Zhang, Wei Wang, Yang Wu, HERB 2.0: an updated database integrating clinical and experimental evidence for traditional Chinese medicine, Nucleic Acids Research, Volume 53, Issue D1, 6 January 2025, Pages D1404–D1414, https://doi.org/10.1093/nar/gkae1037" xr:uid="{27961648-F4DE-47D2-BFA3-2AF1E4E083F4}"/>
-    <hyperlink ref="C5" r:id="rId8" xr:uid="{89E2D2EF-B53E-457A-9117-8C4E24D5992C}"/>
-    <hyperlink ref="B6" r:id="rId9" xr:uid="{7CAA15F8-82F1-4221-BFCF-71ED02EA0686}"/>
-    <hyperlink ref="B7" r:id="rId10" xr:uid="{F5C97B89-1DF4-478C-B201-04CF3855E25A}"/>
-    <hyperlink ref="C7" r:id="rId11" display="Conrad L Schoch, Stacy Ciufo, Mikhail Domrachev, Carol L Hotton, Sivakumar Kannan, Rogneda Khovanskaya, Detlef Leipe, Richard Mcveigh, Kathleen O’Neill, Barbara Robbertse, Shobha Sharma, Vladimir Soussov, John P Sullivan, Lu Sun, Seán Turner, Ilene Karsch-Mizrachi, NCBI Taxonomy: a comprehensive update on curation, resources and tools, Database, Volume 2020, 2020, baaa062, https://doi.org/10.1093/database/baaa062" xr:uid="{47CB1B4F-B1A8-41E4-8312-502E8ECAF9A9}"/>
-    <hyperlink ref="B8" r:id="rId12" xr:uid="{7E0487B4-A4EC-4288-944A-6C9462111A31}"/>
-    <hyperlink ref="B9" r:id="rId13" xr:uid="{E150E2BC-D9FF-4DDD-99E1-F6AC5971B0D3}"/>
-    <hyperlink ref="B10" r:id="rId14" xr:uid="{EA0ECD1D-CF38-4520-9AD0-06AFB73B7A17}"/>
-    <hyperlink ref="B11" r:id="rId15" display="http://bidd2.nus.edu.sg/CMAUP/" xr:uid="{80A088F4-6373-4ABD-9181-EF1431784C50}"/>
-    <hyperlink ref="B12" r:id="rId16" xr:uid="{EF4EF6B3-534D-4ACE-B830-03779F831AB6}"/>
-    <hyperlink ref="B13" r:id="rId17" xr:uid="{C67939E7-70A3-44CC-8FB1-9E19E0395420}"/>
-    <hyperlink ref="B14" r:id="rId18" xr:uid="{E237036F-1269-4824-9244-862303DB1440}"/>
-    <hyperlink ref="B15" r:id="rId19" xr:uid="{F48D8DAA-B1D9-490E-88D1-D01708B7B149}"/>
-    <hyperlink ref="B16" r:id="rId20" xr:uid="{EF1DEBFE-95C6-45C4-8E3E-1BCF05C63AD4}"/>
-    <hyperlink ref="B17" r:id="rId21" xr:uid="{4470D3A7-A658-4341-95B5-3C552C4C03FE}"/>
-    <hyperlink ref="B18" r:id="rId22" xr:uid="{3226CCA7-63F2-43E8-AEB4-C16A6CFFC652}"/>
-    <hyperlink ref="B19" r:id="rId23" xr:uid="{E121C1F7-8584-4E2C-AF1C-70364EA0BAE7}"/>
-    <hyperlink ref="C19" r:id="rId24" display="Steffen Neumann, René Meier, Michael Wenk, Anjana Elapavalore, Takaaki Nishioka, Tobias Schulze, Michael Stravs, Hiroshi Tsugawa, Fumio Matsuda, Emma L Schymanski, MassBank: an open and FAIR mass spectral data resource, Nucleic Acids Research, 2025;, gkaf1193, https://doi.org/10.1093/nar/gkaf1193" xr:uid="{B16FDF65-2438-4C09-9158-4FFCEFFEFE8D}"/>
-    <hyperlink ref="B20" r:id="rId25" xr:uid="{87CB503B-9714-4BD7-BA4B-C7D865F4E9F2}"/>
-    <hyperlink ref="B21" r:id="rId26" xr:uid="{43B51C45-DCC1-4A20-A967-8875D7908666}"/>
-    <hyperlink ref="B22" r:id="rId27" display="https://www-jstor-org.proxy.library.upenn.edu/stable/4253260?searchText=plant+medicine&amp;searchUri=%2Faction%2FdoBasicSearch%3FQuery%3Dplant%2Bmedicine%26so%3Drel&amp;ab_segments=0%2Fbasic_search_gsv2%2Fcontrol&amp;refreqid=fastly-default%3A6b03068ef046aa1576a0a01a1bb5bcc7&amp;seq=1" xr:uid="{B470F1F5-A216-4383-8034-5C09612F02A2}"/>
-    <hyperlink ref="B23" r:id="rId28" display="https://www-jstor-org.proxy.library.upenn.edu/stable/4253157?searchText=plant+medicine&amp;searchUri=%2Faction%2FdoBasicSearch%3FQuery%3Dplant%2Bmedicine%26so%3Drel&amp;ab_segments=0%2Fbasic_search_gsv2%2Fcontrol&amp;refreqid=fastly-default%3A5cbb2cd2072ec5a5282a6cf596d85014&amp;seq=2" xr:uid="{6CEB45FA-2DEE-44C5-9518-EC4039403DF8}"/>
-    <hyperlink ref="B24" r:id="rId29" display="https://www-jstor-org.proxy.library.upenn.edu/stable/23190051?searchText=&amp;searchUri=%2Faction%2FdoBasicSearch%3FQuery%3Dplant%2Bmedicine%26so%3Drel&amp;ab_segments=0%2Fbasic_search_gsv2%2Fcontrol&amp;searchKey=&amp;refreqid=fastly-default%3Ab047ae830c03c8f14834e639e2620d48&amp;initiator=recommender&amp;seq=17" xr:uid="{D419EE3A-0188-4E66-BE59-3D334D3DA176}"/>
-    <hyperlink ref="B25" r:id="rId30" display="https://www-jstor-org.proxy.library.upenn.edu/stable/23187400?searchText=&amp;searchUri=%2Faction%2FdoBasicSearch%3FQuery%3Dplant%2Bmedicine%26so%3Drel&amp;ab_segments=0%2Fbasic_search_gsv2%2Fcontrol&amp;searchKey=&amp;refreqid=fastly-default%3A738f315578184f3680e7a83281dc1131&amp;initiator=recommender&amp;seq=9" xr:uid="{FFEEA725-6E25-473F-8E77-2CA764BF1E7D}"/>
-    <hyperlink ref="F23" r:id="rId31" xr:uid="{3098E61A-05BD-4F48-A4FF-0E03234B1146}"/>
-    <hyperlink ref="F22" r:id="rId32" xr:uid="{4AEADA52-A0F2-411C-BCBD-F61463C1495D}"/>
-    <hyperlink ref="F21" r:id="rId33" xr:uid="{CADDBBC0-F074-4D79-AFA4-6ADCFB28D414}"/>
-    <hyperlink ref="B26" r:id="rId34" xr:uid="{BAEBD2D3-269F-43B9-9D3B-227D513035DF}"/>
-    <hyperlink ref="B27" r:id="rId35" xr:uid="{0DC7B5C5-F0FF-4170-A5A5-9C91A98A9E77}"/>
-    <hyperlink ref="B28" r:id="rId36" xr:uid="{4995F8DE-2512-4976-8E80-49408D9CC0A5}"/>
-    <hyperlink ref="B29" r:id="rId37" xr:uid="{A036A8E9-E937-4CAE-9A54-CB46F874CDF3}"/>
-    <hyperlink ref="B30" r:id="rId38" xr:uid="{49B22F46-B32E-443C-95AF-282562052D39}"/>
-    <hyperlink ref="B31" r:id="rId39" xr:uid="{2DF8A0CA-4023-4B8A-AE66-E49FC37A5449}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{EC3B56C5-8274-496C-BB46-8310F6EB00B5}"/>
+    <hyperlink ref="E3" r:id="rId2" xr:uid="{848D4D3B-8E32-495F-B01F-49C5B717982E}"/>
+    <hyperlink ref="E4" r:id="rId3" xr:uid="{9873785C-418F-4EA0-838A-0A12B2DBA581}"/>
+    <hyperlink ref="E5" r:id="rId4" xr:uid="{FD7B7A15-A769-4289-AF7B-4C9C97DEFC90}"/>
+    <hyperlink ref="G2" r:id="rId5" display="Venkata Chandrasekhar, Kohulan Rajan, Sri Ram Sagar Kanakam, Nisha Sharma, Viktor Weißenborn, Jonas Schaub, Christoph Steinbeck, COCONUT 2.0: a comprehensive overhaul and curation of the collection of open natural products database, Nucleic Acids Research, Volume 53, Issue D1, 6 January 2025, Pages D634–D643, https://doi.org/10.1093/nar/gkae1063" xr:uid="{C1A87BBC-6280-4F1D-8AE2-9ED78A4E86E4}"/>
+    <hyperlink ref="G3" r:id="rId6" display="Kirill Degtyarenko, Paula de Matos, Marcus Ennis, Janna Hastings, Martin Zbinden, Alan McNaught, Rafael Alcántara, Michael Darsow, Mickaël Guedj, Michael Ashburner, ChEBI: a database and ontology for chemical entities of biological interest, Nucleic Acids Research, Volume 36, Issue suppl_1, 1 January 2008, Pages D344–D350, https://doi.org/10.1093/nar/gkm791" xr:uid="{62CD6EEC-6607-4050-904C-77E7C59253BE}"/>
+    <hyperlink ref="G4" r:id="rId7" display="Kai Gao, Liu Liu, Shuangshuang Lei, Zhinong Li, Peipei Huo, Zhihao Wang, Lei Dong, Wenxin Deng, Dechao Bu, Xiaoxi Zeng, Chun Li, Yi Zhao, Wei Zhang, Wei Wang, Yang Wu, HERB 2.0: an updated database integrating clinical and experimental evidence for traditional Chinese medicine, Nucleic Acids Research, Volume 53, Issue D1, 6 January 2025, Pages D1404–D1414, https://doi.org/10.1093/nar/gkae1037" xr:uid="{27961648-F4DE-47D2-BFA3-2AF1E4E083F4}"/>
+    <hyperlink ref="G5" r:id="rId8" xr:uid="{89E2D2EF-B53E-457A-9117-8C4E24D5992C}"/>
+    <hyperlink ref="E6" r:id="rId9" xr:uid="{7CAA15F8-82F1-4221-BFCF-71ED02EA0686}"/>
+    <hyperlink ref="E7" r:id="rId10" xr:uid="{F5C97B89-1DF4-478C-B201-04CF3855E25A}"/>
+    <hyperlink ref="G7" r:id="rId11" display="Conrad L Schoch, Stacy Ciufo, Mikhail Domrachev, Carol L Hotton, Sivakumar Kannan, Rogneda Khovanskaya, Detlef Leipe, Richard Mcveigh, Kathleen O’Neill, Barbara Robbertse, Shobha Sharma, Vladimir Soussov, John P Sullivan, Lu Sun, Seán Turner, Ilene Karsch-Mizrachi, NCBI Taxonomy: a comprehensive update on curation, resources and tools, Database, Volume 2020, 2020, baaa062, https://doi.org/10.1093/database/baaa062" xr:uid="{47CB1B4F-B1A8-41E4-8312-502E8ECAF9A9}"/>
+    <hyperlink ref="E8" r:id="rId12" xr:uid="{7E0487B4-A4EC-4288-944A-6C9462111A31}"/>
+    <hyperlink ref="E9" r:id="rId13" xr:uid="{E150E2BC-D9FF-4DDD-99E1-F6AC5971B0D3}"/>
+    <hyperlink ref="E10" r:id="rId14" xr:uid="{EA0ECD1D-CF38-4520-9AD0-06AFB73B7A17}"/>
+    <hyperlink ref="E11" r:id="rId15" xr:uid="{80A088F4-6373-4ABD-9181-EF1431784C50}"/>
+    <hyperlink ref="E12" r:id="rId16" xr:uid="{EF4EF6B3-534D-4ACE-B830-03779F831AB6}"/>
+    <hyperlink ref="E13" r:id="rId17" xr:uid="{C67939E7-70A3-44CC-8FB1-9E19E0395420}"/>
+    <hyperlink ref="E14" r:id="rId18" xr:uid="{E237036F-1269-4824-9244-862303DB1440}"/>
+    <hyperlink ref="E15" r:id="rId19" xr:uid="{F48D8DAA-B1D9-490E-88D1-D01708B7B149}"/>
+    <hyperlink ref="E16" r:id="rId20" xr:uid="{EF1DEBFE-95C6-45C4-8E3E-1BCF05C63AD4}"/>
+    <hyperlink ref="E17" r:id="rId21" xr:uid="{4470D3A7-A658-4341-95B5-3C552C4C03FE}"/>
+    <hyperlink ref="E18" r:id="rId22" xr:uid="{3226CCA7-63F2-43E8-AEB4-C16A6CFFC652}"/>
+    <hyperlink ref="E19" r:id="rId23" xr:uid="{E121C1F7-8584-4E2C-AF1C-70364EA0BAE7}"/>
+    <hyperlink ref="G19" r:id="rId24" display="Steffen Neumann, René Meier, Michael Wenk, Anjana Elapavalore, Takaaki Nishioka, Tobias Schulze, Michael Stravs, Hiroshi Tsugawa, Fumio Matsuda, Emma L Schymanski, MassBank: an open and FAIR mass spectral data resource, Nucleic Acids Research, 2025;, gkaf1193, https://doi.org/10.1093/nar/gkaf1193" xr:uid="{B16FDF65-2438-4C09-9158-4FFCEFFEFE8D}"/>
+    <hyperlink ref="E20" r:id="rId25" xr:uid="{87CB503B-9714-4BD7-BA4B-C7D865F4E9F2}"/>
+    <hyperlink ref="E21" r:id="rId26" xr:uid="{43B51C45-DCC1-4A20-A967-8875D7908666}"/>
+    <hyperlink ref="E22" r:id="rId27" display="https://www-jstor-org.proxy.library.upenn.edu/stable/4253260?searchText=plant+medicine&amp;searchUri=%2Faction%2FdoBasicSearch%3FQuery%3Dplant%2Bmedicine%26so%3Drel&amp;ab_segments=0%2Fbasic_search_gsv2%2Fcontrol&amp;refreqid=fastly-default%3A6b03068ef046aa1576a0a01a1bb5bcc7&amp;seq=1" xr:uid="{B470F1F5-A216-4383-8034-5C09612F02A2}"/>
+    <hyperlink ref="E23" r:id="rId28" display="https://www-jstor-org.proxy.library.upenn.edu/stable/4253157?searchText=plant+medicine&amp;searchUri=%2Faction%2FdoBasicSearch%3FQuery%3Dplant%2Bmedicine%26so%3Drel&amp;ab_segments=0%2Fbasic_search_gsv2%2Fcontrol&amp;refreqid=fastly-default%3A5cbb2cd2072ec5a5282a6cf596d85014&amp;seq=2" xr:uid="{6CEB45FA-2DEE-44C5-9518-EC4039403DF8}"/>
+    <hyperlink ref="E24" r:id="rId29" display="https://www-jstor-org.proxy.library.upenn.edu/stable/23190051?searchText=&amp;searchUri=%2Faction%2FdoBasicSearch%3FQuery%3Dplant%2Bmedicine%26so%3Drel&amp;ab_segments=0%2Fbasic_search_gsv2%2Fcontrol&amp;searchKey=&amp;refreqid=fastly-default%3Ab047ae830c03c8f14834e639e2620d48&amp;initiator=recommender&amp;seq=17" xr:uid="{D419EE3A-0188-4E66-BE59-3D334D3DA176}"/>
+    <hyperlink ref="E25" r:id="rId30" display="https://www-jstor-org.proxy.library.upenn.edu/stable/23187400?searchText=&amp;searchUri=%2Faction%2FdoBasicSearch%3FQuery%3Dplant%2Bmedicine%26so%3Drel&amp;ab_segments=0%2Fbasic_search_gsv2%2Fcontrol&amp;searchKey=&amp;refreqid=fastly-default%3A738f315578184f3680e7a83281dc1131&amp;initiator=recommender&amp;seq=9" xr:uid="{FFEEA725-6E25-473F-8E77-2CA764BF1E7D}"/>
+    <hyperlink ref="K23" r:id="rId31" xr:uid="{3098E61A-05BD-4F48-A4FF-0E03234B1146}"/>
+    <hyperlink ref="K22" r:id="rId32" xr:uid="{4AEADA52-A0F2-411C-BCBD-F61463C1495D}"/>
+    <hyperlink ref="K21" r:id="rId33" xr:uid="{CADDBBC0-F074-4D79-AFA4-6ADCFB28D414}"/>
+    <hyperlink ref="E26" r:id="rId34" xr:uid="{BAEBD2D3-269F-43B9-9D3B-227D513035DF}"/>
+    <hyperlink ref="E27" r:id="rId35" xr:uid="{0DC7B5C5-F0FF-4170-A5A5-9C91A98A9E77}"/>
+    <hyperlink ref="E28" r:id="rId36" xr:uid="{4995F8DE-2512-4976-8E80-49408D9CC0A5}"/>
+    <hyperlink ref="E29" r:id="rId37" xr:uid="{A036A8E9-E937-4CAE-9A54-CB46F874CDF3}"/>
+    <hyperlink ref="E30" r:id="rId38" xr:uid="{49B22F46-B32E-443C-95AF-282562052D39}"/>
+    <hyperlink ref="E31" r:id="rId39" xr:uid="{2DF8A0CA-4023-4B8A-AE66-E49FC37A5449}"/>
+    <hyperlink ref="G34" r:id="rId40" display="http://iris.wpro.who.int/handle/10665.1/6738" xr:uid="{ED92C355-55B4-4780-AD0F-49F6EF33E172}"/>
+    <hyperlink ref="K35" r:id="rId41" display="https://www.rain-tree.com/copy.htm" xr:uid="{1BB3CBCA-59A2-4C64-AA97-B0DB6CC779A3}"/>
+    <hyperlink ref="E32" r:id="rId42" xr:uid="{AB02F665-B1F5-4A16-97F0-C6D7EC247806}"/>
+    <hyperlink ref="E33" r:id="rId43" xr:uid="{188FE518-BA06-4A2E-8F9A-6E2AB3E156A7}"/>
+    <hyperlink ref="E34" r:id="rId44" xr:uid="{480A54EC-0090-4BB2-8877-FBD27905842A}"/>
+    <hyperlink ref="E35" r:id="rId45" xr:uid="{944DD57D-6054-446C-8A3C-0023E5B9F84C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId40"/>
+  <pageSetup orientation="portrait" r:id="rId46"/>
 </worksheet>
 </file>
--- a/doc/POPPy.xlsx
+++ b/doc/POPPy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oreil\Documents\GitHub\poppy\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59889556-175D-48ED-9403-C538195FE684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F84517-BFE9-4D83-8D87-3F4F2651E083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="327">
   <si>
     <t>Database</t>
   </si>
@@ -309,9 +309,6 @@
     <t xml:space="preserve">Creative Commons Attribution 4.0 International License </t>
   </si>
   <si>
-    <t xml:space="preserve">Downloadable links to pages with text of code information </t>
-  </si>
-  <si>
     <t>Kinda- protien sequences and functional info</t>
   </si>
   <si>
@@ -430,9 +427,6 @@
   </si>
   <si>
     <t>Creative Commons CC0</t>
-  </si>
-  <si>
-    <t>Dataset able to be downloaded</t>
   </si>
   <si>
     <t>Chemical ID, chemical name</t>
@@ -1182,109 +1176,146 @@
     <t>https://www.stuartxchange.org/CompleteList.html</t>
   </si>
   <si>
+    <t xml:space="preserve">Philippine Medicinal Plants </t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Data Format</t>
+  </si>
+  <si>
+    <t>Still Available?</t>
+  </si>
+  <si>
+    <t>PubMed ID</t>
+  </si>
+  <si>
+    <t>Identifiers</t>
+  </si>
+  <si>
+    <t>Phytochemical- general</t>
+  </si>
+  <si>
+    <t>Biomedical- general</t>
+  </si>
+  <si>
+    <t>Online Database</t>
+  </si>
+  <si>
+    <t>No PubMed article</t>
+  </si>
+  <si>
+    <t>Plant taxonomy- medicinal</t>
+  </si>
+  <si>
+    <t>Plant taxonomy- general</t>
+  </si>
+  <si>
+    <t>http://bidd2.nus.edu.sg/CMAUP/</t>
+  </si>
+  <si>
+    <t>Journal Article</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.who.int/publications/i/item/9290611200 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://files.spiritmaji.com/books/diet-herbal-ayurveda-remedies/Handbook%20of%20Ayurvedic%20Medicinal%20-%20L.D.%20Kapoor.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://iris.who.int/items/a381e797-ac83-4601-a845-45890ef76413 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rain-tree.com/plants.htm </t>
+  </si>
+  <si>
+    <t>Downloadable dataset, suplementary data table (apparently)</t>
+  </si>
+  <si>
+    <t>Downloadable links to pages with text of code information, downloads as H5 files</t>
+  </si>
+  <si>
+    <t>Dataset able to be downloaded but it is within each search "topic" not the whole database in one download. It is available in CSV and XLSX formats.</t>
+  </si>
+  <si>
+    <t>Downloadable links, some download as excel spreadsheets, some as CSV files</t>
+  </si>
+  <si>
+    <t>Downloadable PDF</t>
+  </si>
+  <si>
+    <t>Kinda- gives some constituents of the plant</t>
+  </si>
+  <si>
+    <t>Kinda- through the uses section</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (family, common names, scientific names, other vernacular names, general info, botany, distribution, constituents, properties, toxicity, parts used, uses, studies, availability)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Philippines </t>
+  </si>
+  <si>
+    <t>I couldn't find anywhere to download information and the copyright info page suggests that downloads were removed because people kept stealing the info</t>
+  </si>
+  <si>
+    <t>Just talks  about how info got stolen and how the author is mad about it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harindran, Jyoti. (2016). An illustrated compilation of Philippine medicinal plants by Dr Godofredo Stuart. 10.13140/RG.2.2.11918.36160. </t>
+  </si>
+  <si>
+    <t>Plant Species in the Folk medicine of Kit Mikayi Region, Western Kenya</t>
+  </si>
+  <si>
+    <t>https://opensiuc.lib.siu.edu/cgi/viewcontent.cgi?article=1672&amp;context=ebl</t>
+  </si>
+  <si>
+    <t>Western Kenya</t>
+  </si>
+  <si>
+    <t>Able to download content but not modify, can not  use info in combination with an AI tool</t>
+  </si>
+  <si>
     <r>
-      <t>© All content, imagery, and photos are copyrighted / </t>
+      <t>Phanuel, Arwa S.; O., Nyunja R.; and C., Onyango J. (2010) "Plant Species in the Folk medicine of Kit Mikayi Region, Western Kenya," </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FF0000FF"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
-      <t>Godofredo U. Stuart, Jr., MD</t>
+      <t>Ethnobotanical Leaflets</t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="7"/>
+        <sz val="11"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
-      <t> • </t>
+      <t>: Vol. 2010: Iss. 7, Article 13. Available at: https://opensiuc.lib.siu.edu/ebl/vol2010/iss7/13</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="7"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>StuartXchange</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Philippine Medicinal Plants </t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Data Format</t>
-  </si>
-  <si>
-    <t>Still Available?</t>
-  </si>
-  <si>
-    <t>PubMed ID</t>
-  </si>
-  <si>
-    <t>Identifiers</t>
-  </si>
-  <si>
-    <t>Phytochemical- general</t>
-  </si>
-  <si>
-    <t>Biomedical- general</t>
-  </si>
-  <si>
-    <t>Online Database</t>
-  </si>
-  <si>
-    <t>No PubMed article</t>
-  </si>
-  <si>
-    <t>Plant taxonomy- medicinal</t>
-  </si>
-  <si>
-    <t>Plant taxonomy- general</t>
-  </si>
-  <si>
-    <t>http://bidd2.nus.edu.sg/CMAUP/</t>
-  </si>
-  <si>
-    <t>Journal Article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.who.int/publications/i/item/9290611200 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://files.spiritmaji.com/books/diet-herbal-ayurveda-remedies/Handbook%20of%20Ayurvedic%20Medicinal%20-%20L.D.%20Kapoor.pdf </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://iris.who.int/items/a381e797-ac83-4601-a845-45890ef76413 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.rain-tree.com/plants.htm </t>
-  </si>
-  <si>
-    <t>Downloadable dataset, suplementary data table (apparently)</t>
-  </si>
-  <si>
-    <t>Downloadable links to pages with text of code information, downloads as H5 files</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (plant name, uses, part used, family name)</t>
+  </si>
+  <si>
+    <t>© All content, imagery, and photos are copyrighted / Godofredo U. Stuart, Jr., MD • StuartXchange</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1398,31 +1429,21 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="7"/>
+      <sz val="6"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <color rgb="FF212121"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF212121"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1480,7 +1501,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1529,17 +1550,13 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1547,7 +1564,176 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1877,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S37"/>
+  <dimension ref="A1:S38"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.1796875" style="7"/>
@@ -1896,28 +2082,28 @@
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>3</v>
@@ -1941,7 +2127,7 @@
         <v>9</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>10</v>
@@ -1958,13 +2144,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>14</v>
@@ -1975,7 +2161,7 @@
       <c r="G2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="23">
         <v>39588778</v>
       </c>
       <c r="I2" s="6" t="s">
@@ -2017,13 +2203,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>27</v>
@@ -2034,7 +2220,7 @@
       <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="23">
         <v>17932057</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -2076,13 +2262,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>37</v>
@@ -2093,7 +2279,7 @@
       <c r="G4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="23">
         <v>39558177</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -2129,13 +2315,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>49</v>
@@ -2146,7 +2332,7 @@
       <c r="G5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="23">
         <v>14681407</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -2188,13 +2374,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>58</v>
@@ -2203,10 +2389,10 @@
         <v>24</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>59</v>
@@ -2218,7 +2404,7 @@
         <v>60</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>33</v>
@@ -2247,13 +2433,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>66</v>
@@ -2264,7 +2450,7 @@
       <c r="G7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="23">
         <v>32761142</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -2306,13 +2492,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>75</v>
@@ -2321,9 +2507,9 @@
         <v>33</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="H8" s="25">
+        <v>264</v>
+      </c>
+      <c r="H8" s="23">
         <v>17989687</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -2362,13 +2548,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>83</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>84</v>
@@ -2379,7 +2565,7 @@
       <c r="G9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="23">
         <v>39552041</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -2392,7 +2578,7 @@
         <v>88</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>33</v>
@@ -2401,7 +2587,7 @@
         <v>24</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P9" s="7" t="s">
         <v>56</v>
@@ -2421,40 +2607,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C10" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="H10" s="23">
+        <v>32117874</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="H10" s="25">
-        <v>32117874</v>
-      </c>
-      <c r="I10" s="6" t="s">
+      <c r="J10" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="L10" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="M10" s="6" t="s">
         <v>97</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>24</v>
@@ -2463,10 +2649,10 @@
         <v>33</v>
       </c>
       <c r="P10" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q10" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="Q10" s="6" t="s">
-        <v>100</v>
       </c>
       <c r="R10" s="7" t="s">
         <v>25</v>
@@ -2475,45 +2661,45 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="154.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:19" ht="154" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E11" s="26" t="s">
-        <v>305</v>
+        <v>298</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>302</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G11" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="23">
+        <v>30357356</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="H11" s="25">
-        <v>30357356</v>
-      </c>
-      <c r="I11" s="6" t="s">
+      <c r="N11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O11" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="N11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O11" s="7" t="s">
+      <c r="Q11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R11" s="7" t="s">
         <v>104</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="R11" s="7" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="140" x14ac:dyDescent="0.3">
@@ -2521,49 +2707,49 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="H12" s="6">
         <v>35616633</v>
       </c>
       <c r="I12" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="L12" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="M12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="M12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N12" s="6" t="s">
+      <c r="O12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>113</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="Q12" s="7" t="s">
         <v>24</v>
@@ -2575,104 +2761,104 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="168" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" ht="170" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7">
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="23">
+        <v>41243954</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="H13" s="25">
-        <v>41243954</v>
-      </c>
-      <c r="I13" s="6" t="s">
+      <c r="L13" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="M13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N13" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="M13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N13" s="6" t="s">
+      <c r="O13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="O13" s="7" t="s">
+      <c r="P13" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="P13" s="6" t="s">
+      <c r="Q13" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="Q13" s="6" t="s">
-        <v>123</v>
       </c>
       <c r="R13" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" ht="103" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H14" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="I14" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>302</v>
-      </c>
-      <c r="I14" s="6" t="s">
+      <c r="J14" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="K14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="L14" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P14" s="7" t="s">
         <v>129</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>131</v>
       </c>
       <c r="Q14" s="7" t="s">
         <v>24</v>
@@ -2681,7 +2867,7 @@
         <v>25</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="93.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2689,43 +2875,43 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="H15" s="11" t="s">
+        <v>299</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="11" t="s">
+      <c r="J15" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="I15" s="6" t="s">
+      <c r="K15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="L15" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N15" s="7" t="s">
         <v>137</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="M15" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>139</v>
       </c>
       <c r="O15" s="7" t="s">
         <v>24</v>
@@ -2737,7 +2923,7 @@
         <v>24</v>
       </c>
       <c r="R15" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="126" x14ac:dyDescent="0.3">
@@ -2745,49 +2931,49 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C16" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="H16" s="23">
+        <v>24735618</v>
+      </c>
+      <c r="I16" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="J16" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="H16" s="25">
-        <v>24735618</v>
-      </c>
-      <c r="I16" s="6" t="s">
+      <c r="K16" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="J16" s="7" t="s">
+      <c r="L16" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="M16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N16" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="O16" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="M16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N16" s="7" t="s">
+      <c r="P16" s="6" t="s">
         <v>148</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q16" s="7" t="s">
         <v>33</v>
@@ -2804,55 +2990,55 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="H17" s="23">
+        <v>36910986</v>
+      </c>
+      <c r="I17" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="14" t="s">
+      <c r="J17" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="H17" s="25">
-        <v>36910986</v>
-      </c>
-      <c r="I17" s="6" t="s">
+      <c r="K17" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="L17" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="M17" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N17" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="O17" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="M17" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N17" s="7" t="s">
+      <c r="P17" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="O17" s="7" t="s">
+      <c r="Q17" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="R17" s="7" t="s">
         <v>159</v>
-      </c>
-      <c r="Q17" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="R17" s="7" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="126" x14ac:dyDescent="0.3">
@@ -2860,28 +3046,28 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E18" s="15" t="s">
+      <c r="H18" s="23">
+        <v>39558165</v>
+      </c>
+      <c r="I18" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="H18" s="25">
-        <v>39558165</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>69</v>
@@ -2890,22 +3076,22 @@
         <v>70</v>
       </c>
       <c r="L18" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="M18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O18" s="7" t="s">
+      <c r="Q18" s="6" t="s">
         <v>167</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q18" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="R18" s="7" t="s">
         <v>25</v>
@@ -2916,34 +3102,34 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E19" s="15" t="s">
+      <c r="H19" s="23">
+        <v>41217946</v>
+      </c>
+      <c r="I19" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="16" t="s">
+      <c r="J19" s="17" t="s">
         <v>172</v>
       </c>
-      <c r="H19" s="25">
-        <v>41217946</v>
-      </c>
-      <c r="I19" s="6" t="s">
+      <c r="L19" s="6" t="s">
         <v>173</v>
-      </c>
-      <c r="J19" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>175</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>33</v>
@@ -2955,7 +3141,7 @@
         <v>33</v>
       </c>
       <c r="P19" s="6" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="Q19" s="7" t="s">
         <v>24</v>
@@ -2972,34 +3158,37 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="C20" s="17" t="s">
+      <c r="E20" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="15" t="s">
+      <c r="H20" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I20" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="J20" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K20" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="K20" s="20" t="s">
-        <v>181</v>
+      <c r="L20" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>33</v>
@@ -3017,7 +3206,7 @@
         <v>33</v>
       </c>
       <c r="R20" s="7" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="98" x14ac:dyDescent="0.3">
@@ -3025,34 +3214,37 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="E21" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E21" s="15" t="s">
+      <c r="H21" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I21" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="6" t="s">
+      <c r="J21" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K21" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="J21" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>187</v>
+      <c r="L21" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>33</v>
@@ -3070,7 +3262,7 @@
         <v>24</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="S21" s="7">
         <v>2010</v>
@@ -3081,34 +3273,37 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="E22" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="E22" s="15" t="s">
+      <c r="H22" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I22" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="J22" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K22" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>192</v>
+      <c r="L22" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>33</v>
@@ -3126,7 +3321,7 @@
         <v>24</v>
       </c>
       <c r="R22" s="7" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="S22" s="7">
         <v>1971</v>
@@ -3137,34 +3332,37 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="E23" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="E23" s="15" t="s">
+      <c r="H23" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I23" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F23" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="6" t="s">
+      <c r="J23" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K23" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="J23" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>198</v>
+      <c r="L23" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>33</v>
@@ -3182,7 +3380,7 @@
         <v>33</v>
       </c>
       <c r="R23" s="7" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="S23" s="7">
         <v>1970</v>
@@ -3193,34 +3391,37 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="E24" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="F24" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="D24" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="E24" s="15" t="s">
+      <c r="H24" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I24" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="J24" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="K24" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J24" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="K24" s="20" t="s">
-        <v>204</v>
+      <c r="L24" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>33</v>
@@ -3238,7 +3439,7 @@
         <v>33</v>
       </c>
       <c r="R24" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="98" x14ac:dyDescent="0.3">
@@ -3246,34 +3447,37 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C25" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>306</v>
-      </c>
-      <c r="E25" s="15" t="s">
+      <c r="J25" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>209</v>
-      </c>
       <c r="K25" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>312</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>33</v>
@@ -3288,10 +3492,10 @@
         <v>56</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="R25" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="84" x14ac:dyDescent="0.3">
@@ -3299,31 +3503,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C26" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I26" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="D26" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E26" s="15" t="s">
+      <c r="J26" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F26" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="I26" s="6" t="s">
+      <c r="L26" s="6" t="s">
         <v>214</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>216</v>
       </c>
       <c r="M26" s="7" t="s">
         <v>33</v>
@@ -3338,10 +3542,10 @@
         <v>56</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="R26" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="S26" s="7">
         <v>2026</v>
@@ -3352,34 +3556,34 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C27" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I27" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E27" s="15" t="s">
+      <c r="J27" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="F27" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="I27" s="6" t="s">
+      <c r="K27" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="J27" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="K27" s="6" t="s">
+      <c r="L27" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>225</v>
       </c>
       <c r="M27" s="7" t="s">
         <v>24</v>
@@ -3388,16 +3592,16 @@
         <v>33</v>
       </c>
       <c r="O27" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q27" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="P27" s="6" t="s">
+      <c r="R27" s="7" t="s">
         <v>227</v>
-      </c>
-      <c r="Q27" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="R27" s="7" t="s">
-        <v>229</v>
       </c>
       <c r="S27" s="7">
         <v>1989</v>
@@ -3408,43 +3612,43 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C28" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="D28" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E28" s="15" t="s">
+      <c r="H28" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="I28" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F28" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="18" t="s">
+      <c r="J28" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="H28" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="I28" s="6" t="s">
+      <c r="K28" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="L28" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="M28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N28" s="7" t="s">
         <v>235</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>237</v>
       </c>
       <c r="O28" s="7" t="s">
         <v>24</v>
@@ -3453,10 +3657,10 @@
         <v>56</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="S28" s="7">
         <v>2014</v>
@@ -3467,37 +3671,37 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>224</v>
-      </c>
-      <c r="E29" s="15" t="s">
+      <c r="H29" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="I29" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="6" t="s">
+      <c r="J29" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I29" s="6" t="s">
+      <c r="K29" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="L29" s="6" t="s">
         <v>244</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>246</v>
       </c>
       <c r="M29" s="7" t="s">
         <v>24</v>
@@ -3506,16 +3710,16 @@
         <v>33</v>
       </c>
       <c r="O29" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q29" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="P29" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q29" s="6" t="s">
-        <v>249</v>
-      </c>
       <c r="R29" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="S29" s="7">
         <v>2007</v>
@@ -3526,34 +3730,34 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C30" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I30" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D30" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E30" s="15" t="s">
+      <c r="J30" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="I30" s="6" t="s">
+      <c r="K30" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="J30" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>254</v>
-      </c>
       <c r="L30" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M30" s="7" t="s">
         <v>24</v>
@@ -3562,16 +3766,16 @@
         <v>33</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="R30" s="7" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="S30" s="7">
         <v>2016</v>
@@ -3582,34 +3786,34 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I31" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E31" s="15" t="s">
+      <c r="K31" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="F31" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="I31" s="6" t="s">
+      <c r="M31" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="K31" s="19" t="s">
+      <c r="N31" s="7" t="s">
         <v>260</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>262</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>24</v>
@@ -3627,39 +3831,39 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="98.5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" ht="98" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>307</v>
+        <v>222</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>304</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="I32" s="22" t="s">
-        <v>270</v>
+        <v>299</v>
+      </c>
+      <c r="I32" s="21" t="s">
+        <v>268</v>
       </c>
       <c r="K32" s="7" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="M32" s="7" t="s">
         <v>24</v>
@@ -3677,45 +3881,45 @@
         <v>24</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="S32" s="7">
         <v>1998</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="84.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19" ht="84" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C33" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>273</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="D33" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>308</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>275</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>274</v>
-      </c>
       <c r="K33" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M33" s="7" t="s">
         <v>24</v>
@@ -3724,54 +3928,54 @@
         <v>33</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="P33" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="S33" s="7">
         <v>2001</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="126.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" ht="126" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C34" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>306</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="K34" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D34" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>309</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G34" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>284</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>278</v>
-      </c>
       <c r="L34" s="6" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="M34" s="7" t="s">
         <v>24</v>
@@ -3780,57 +3984,57 @@
         <v>33</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="S34" s="7">
         <v>1998</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="112.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" ht="112" x14ac:dyDescent="0.3">
       <c r="A35" s="7">
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C35" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G35" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="I35" s="6" t="s">
+      <c r="J35" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="J35" s="6" t="s">
-        <v>289</v>
-      </c>
       <c r="K35" s="16" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L35" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M35" s="7" t="s">
         <v>33</v>
@@ -3842,36 +4046,151 @@
         <v>33</v>
       </c>
       <c r="P35" s="7" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="Q35" s="7" t="s">
         <v>33</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="S35" s="7">
         <v>2025</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" ht="98" x14ac:dyDescent="0.3">
       <c r="A36" s="7">
         <v>35</v>
       </c>
+      <c r="B36" s="6" t="s">
+        <v>300</v>
+      </c>
       <c r="C36" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>298</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>290</v>
+        <v>288</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>318</v>
       </c>
       <c r="K36" s="24" t="s">
-        <v>291</v>
+        <v>326</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O36" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="P36" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q36" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="S36" s="7">
+        <v>2025</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="J37" s="21"/>
+    <row r="37" spans="1:19" ht="112" x14ac:dyDescent="0.3">
+      <c r="A37" s="7">
+        <v>36</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="J37" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P37" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A38" s="7">
+        <v>37</v>
+      </c>
+      <c r="G38" s="22"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Phytochemical- general">
+      <formula>NOT(ISERROR(SEARCH("Phytochemical- general",B1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Biomedical- general">
+      <formula>NOT(ISERROR(SEARCH("Biomedical- general",B1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Plant taxonomy- medicinal">
+      <formula>NOT(ISERROR(SEARCH("Plant taxonomy- medicinal",B1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Plant taxonomy- general">
+      <formula>NOT(ISERROR(SEARCH("Plant taxonomy- general",B1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{EC3B56C5-8274-496C-BB46-8310F6EB00B5}"/>
     <hyperlink ref="E3" r:id="rId2" xr:uid="{848D4D3B-8E32-495F-B01F-49C5B717982E}"/>

--- a/doc/POPPy.xlsx
+++ b/doc/POPPy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oreil\Documents\GitHub\poppy\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2F84517-BFE9-4D83-8D87-3F4F2651E083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49512DF8-C64E-4CCD-B8C0-25A8A4FD6A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="348">
   <si>
     <t>Database</t>
   </si>
@@ -1173,9 +1173,6 @@
     <t>You have to get written authorization from the author to use, transmit, or reproduce the database (There is educational exceptions but I'm not sure if this would count)</t>
   </si>
   <si>
-    <t>https://www.stuartxchange.org/CompleteList.html</t>
-  </si>
-  <si>
     <t xml:space="preserve">Philippine Medicinal Plants </t>
   </si>
   <si>
@@ -1272,13 +1269,7 @@
     <t>Plant Species in the Folk medicine of Kit Mikayi Region, Western Kenya</t>
   </si>
   <si>
-    <t>https://opensiuc.lib.siu.edu/cgi/viewcontent.cgi?article=1672&amp;context=ebl</t>
-  </si>
-  <si>
     <t>Western Kenya</t>
-  </si>
-  <si>
-    <t>Able to download content but not modify, can not  use info in combination with an AI tool</t>
   </si>
   <si>
     <r>
@@ -1309,6 +1300,78 @@
   </si>
   <si>
     <t>© All content, imagery, and photos are copyrighted / Godofredo U. Stuart, Jr., MD • StuartXchange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opensiuc.lib.siu.edu/cgi/viewcontent.cgi?article=1672&amp;context=ebl </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.stuartxchange.org/CompleteList.html </t>
+  </si>
+  <si>
+    <t>https://www.knapsackfamily.com/knapsack_core/top.php</t>
+  </si>
+  <si>
+    <t>KNApSAcK</t>
+  </si>
+  <si>
+    <t>© 2007 NARA INSTITUTE of SCIENCE and TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>Common names, formula, CAS RN, C_ID, InChIKey, InChICode, SMILES)</t>
+  </si>
+  <si>
+    <t>Yes, 24,776 species- includes animals, bacteria, fungi as well but it does specify which of these catagories an organism is</t>
+  </si>
+  <si>
+    <t>Yes, 63,735</t>
+  </si>
+  <si>
+    <t>Nakamura Y, Afendi FM, Parvin AK, Ono N, Tanaka K, Hirai Morita A, Sato T, Sugiura T, Altaf-Ul-Amin M, Kanaya S. KNApSAcK Metabolite Activity Database for retrieving the relationships between metabolites and biological activities. Plant Cell Physiol. 2014 Jan;55(1):e7. doi: 10.1093/pcp/pct176. Epub 2013 Nov 27. PMID: 24285751.</t>
+  </si>
+  <si>
+    <t>Binding DB</t>
+  </si>
+  <si>
+    <t>https://www.bindingdb.org/rwd/bind/index.jsp</t>
+  </si>
+  <si>
+    <t>Provides info on different compounds as well as the organisms they are found in, you can also search the organism name and get a list of the compounds present in that organism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creativecommons attribution 3.0 lisence </t>
+  </si>
+  <si>
+    <t>Free to share and adapt but you must give appropriate credit</t>
+  </si>
+  <si>
+    <t>Kinda- gives FDA drugs with compound</t>
+  </si>
+  <si>
+    <t>Common name, SMILES, InChI</t>
+  </si>
+  <si>
+    <t>Able to download files in TSV or Sdfile formats</t>
+  </si>
+  <si>
+    <t>Provides info on different compounds (name, chemical structure pathways, chemical structure, data, targets, publications, special datasets)</t>
+  </si>
+  <si>
+    <t>Chen X, Liu M, Gilson MK. BindingDB: a web-accessible molecular recognition database. Comb Chem High Throughput Screen. 2001 Dec;4(8):719-25. doi: 10.2174/1386207013330670. PMID: 11812264.</t>
+  </si>
+  <si>
+    <t>PhytoHub</t>
+  </si>
+  <si>
+    <t>https://phytohub.eu/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provides info on food phytochemicals, known metabolites, and predicted metabolites </t>
+  </si>
+  <si>
+    <t>Kinda- some of the food sources are plants</t>
+  </si>
+  <si>
+    <t>PhytoHub ID, name, systematic name, synonyms, CAS number, chemical formula, IUPAC name, InChI Key, InChI identifier, SMILES</t>
   </si>
 </sst>
 </file>
@@ -1429,12 +1492,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="6"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF212121"/>
       <name val="Times New Roman"/>
@@ -1442,6 +1499,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF202020"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1501,7 +1564,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1552,9 +1615,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2063,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S40"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.1796875" style="7"/>
@@ -2082,28 +2150,28 @@
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>3</v>
@@ -2127,7 +2195,7 @@
         <v>9</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>10</v>
@@ -2144,13 +2212,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>14</v>
@@ -2161,7 +2229,7 @@
       <c r="G2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="23">
+      <c r="H2" s="22">
         <v>39588778</v>
       </c>
       <c r="I2" s="6" t="s">
@@ -2203,13 +2271,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>27</v>
@@ -2220,7 +2288,7 @@
       <c r="G3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="23">
+      <c r="H3" s="22">
         <v>17932057</v>
       </c>
       <c r="I3" s="6" t="s">
@@ -2262,13 +2330,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>37</v>
@@ -2279,7 +2347,7 @@
       <c r="G4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="23">
+      <c r="H4" s="22">
         <v>39558177</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -2315,13 +2383,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>49</v>
@@ -2332,7 +2400,7 @@
       <c r="G5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="23">
+      <c r="H5" s="22">
         <v>14681407</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -2374,13 +2442,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>58</v>
@@ -2392,7 +2460,7 @@
         <v>263</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>59</v>
@@ -2404,7 +2472,7 @@
         <v>60</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>33</v>
@@ -2433,13 +2501,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>65</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>66</v>
@@ -2450,7 +2518,7 @@
       <c r="G7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="23">
+      <c r="H7" s="22">
         <v>32761142</v>
       </c>
       <c r="I7" s="6" t="s">
@@ -2492,13 +2560,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>75</v>
@@ -2509,7 +2577,7 @@
       <c r="G8" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="22">
         <v>17989687</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -2548,13 +2616,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>83</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>84</v>
@@ -2565,7 +2633,7 @@
       <c r="G9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="23">
+      <c r="H9" s="22">
         <v>39552041</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -2578,7 +2646,7 @@
         <v>88</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>33</v>
@@ -2607,13 +2675,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>90</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>91</v>
@@ -2624,7 +2692,7 @@
       <c r="G10" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="23">
+      <c r="H10" s="22">
         <v>32117874</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -2666,16 +2734,16 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>100</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>24</v>
@@ -2683,7 +2751,7 @@
       <c r="G11" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="23">
+      <c r="H11" s="22">
         <v>30357356</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -2707,13 +2775,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>105</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>106</v>
@@ -2766,13 +2834,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>114</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>115</v>
@@ -2783,7 +2851,7 @@
       <c r="G13" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="22">
         <v>41243954</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -2816,13 +2884,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>123</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>124</v>
@@ -2834,7 +2902,7 @@
         <v>125</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I14" s="6" t="s">
         <v>126</v>
@@ -2846,7 +2914,7 @@
         <v>128</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>33</v>
@@ -2875,13 +2943,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>131</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>132</v>
@@ -2893,7 +2961,7 @@
         <v>133</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>134</v>
@@ -2905,7 +2973,7 @@
         <v>136</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>33</v>
@@ -2931,13 +2999,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>139</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>140</v>
@@ -2948,7 +3016,7 @@
       <c r="G16" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="22">
         <v>24735618</v>
       </c>
       <c r="I16" s="6" t="s">
@@ -2990,13 +3058,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C17" s="13" t="s">
         <v>265</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>149</v>
@@ -3007,7 +3075,7 @@
       <c r="G17" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="H17" s="23">
+      <c r="H17" s="22">
         <v>36910986</v>
       </c>
       <c r="I17" s="6" t="s">
@@ -3046,13 +3114,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E18" s="15" t="s">
         <v>161</v>
@@ -3063,7 +3131,7 @@
       <c r="G18" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="22">
         <v>39558165</v>
       </c>
       <c r="I18" s="6" t="s">
@@ -3102,13 +3170,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>168</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>169</v>
@@ -3119,7 +3187,7 @@
       <c r="G19" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="22">
         <v>41217946</v>
       </c>
       <c r="I19" s="6" t="s">
@@ -3158,13 +3226,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>175</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>176</v>
@@ -3176,7 +3244,7 @@
         <v>177</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>178</v>
@@ -3188,7 +3256,7 @@
         <v>179</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>33</v>
@@ -3214,13 +3282,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>181</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>182</v>
@@ -3232,7 +3300,7 @@
         <v>183</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I21" s="6" t="s">
         <v>184</v>
@@ -3244,7 +3312,7 @@
         <v>185</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>33</v>
@@ -3273,13 +3341,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>187</v>
@@ -3291,7 +3359,7 @@
         <v>188</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>189</v>
@@ -3303,7 +3371,7 @@
         <v>190</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>33</v>
@@ -3332,13 +3400,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>192</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E23" s="15" t="s">
         <v>193</v>
@@ -3350,7 +3418,7 @@
         <v>194</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I23" s="6" t="s">
         <v>195</v>
@@ -3362,7 +3430,7 @@
         <v>196</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>33</v>
@@ -3391,13 +3459,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>198</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E24" s="15" t="s">
         <v>199</v>
@@ -3409,7 +3477,7 @@
         <v>200</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>201</v>
@@ -3421,7 +3489,7 @@
         <v>202</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>33</v>
@@ -3447,13 +3515,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C25" s="17" t="s">
         <v>204</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E25" s="15" t="s">
         <v>205</v>
@@ -3465,7 +3533,7 @@
         <v>266</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I25" s="6" t="s">
         <v>206</v>
@@ -3477,7 +3545,7 @@
         <v>202</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>33</v>
@@ -3503,13 +3571,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>210</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E26" s="15" t="s">
         <v>211</v>
@@ -3518,7 +3586,7 @@
         <v>33</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>212</v>
@@ -3556,7 +3624,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>217</v>
@@ -3571,7 +3639,7 @@
         <v>33</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I27" s="6" t="s">
         <v>219</v>
@@ -3612,13 +3680,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>228</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E28" s="15" t="s">
         <v>229</v>
@@ -3630,7 +3698,7 @@
         <v>230</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>231</v>
@@ -3671,7 +3739,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>238</v>
@@ -3689,7 +3757,7 @@
         <v>240</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I29" s="6" t="s">
         <v>241</v>
@@ -3730,7 +3798,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>248</v>
@@ -3745,7 +3813,7 @@
         <v>33</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>250</v>
@@ -3786,13 +3854,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>255</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E31" s="15" t="s">
         <v>256</v>
@@ -3801,7 +3869,7 @@
         <v>33</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I31" s="6" t="s">
         <v>257</v>
@@ -3836,7 +3904,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>261</v>
@@ -3845,7 +3913,7 @@
         <v>222</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>33</v>
@@ -3854,7 +3922,7 @@
         <v>269</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I32" s="21" t="s">
         <v>268</v>
@@ -3892,7 +3960,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>270</v>
@@ -3901,7 +3969,7 @@
         <v>222</v>
       </c>
       <c r="E33" s="15" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>33</v>
@@ -3910,7 +3978,7 @@
         <v>273</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>272</v>
@@ -3948,7 +4016,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>274</v>
@@ -3957,7 +4025,7 @@
         <v>222</v>
       </c>
       <c r="E34" s="15" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>33</v>
@@ -3966,7 +4034,7 @@
         <v>275</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>282</v>
@@ -4004,16 +4072,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>283</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E35" s="15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>33</v>
@@ -4022,7 +4090,7 @@
         <v>286</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I35" s="6" t="s">
         <v>285</v>
@@ -4063,37 +4131,37 @@
         <v>35</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D36" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="H36" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="E36" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>299</v>
-      </c>
       <c r="I36" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="J36" s="6" t="s">
-        <v>318</v>
-      </c>
-      <c r="K36" s="24" t="s">
-        <v>326</v>
+        <v>317</v>
+      </c>
+      <c r="K36" s="23" t="s">
+        <v>323</v>
       </c>
       <c r="L36" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="M36" s="7" t="s">
         <v>33</v>
@@ -4102,16 +4170,16 @@
         <v>33</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P36" s="7" t="s">
         <v>246</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S36" s="7">
         <v>2025</v>
@@ -4122,34 +4190,32 @@
         <v>36</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="E37" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>324</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G37" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G37" s="17" t="s">
-        <v>324</v>
-      </c>
       <c r="H37" s="7" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="J37" s="21" t="s">
-        <v>323</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="J37" s="21"/>
       <c r="L37" s="7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="M37" s="7" t="s">
         <v>33</v>
@@ -4167,14 +4233,155 @@
         <v>33</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" ht="140" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>37</v>
       </c>
-      <c r="G38" s="22"/>
+      <c r="B38" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="H38" s="22">
+        <v>24285751</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="K38" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N38" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="O38" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R38" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S38" s="7">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="98" x14ac:dyDescent="0.3">
+      <c r="A39" s="7">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="H39" s="22">
+        <v>11812264</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P39" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="Q39" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="R39" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" s="7">
+        <v>39</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="O40" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P40" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="Q40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R40" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
@@ -4237,8 +4444,10 @@
     <hyperlink ref="E33" r:id="rId43" xr:uid="{188FE518-BA06-4A2E-8F9A-6E2AB3E156A7}"/>
     <hyperlink ref="E34" r:id="rId44" xr:uid="{480A54EC-0090-4BB2-8877-FBD27905842A}"/>
     <hyperlink ref="E35" r:id="rId45" xr:uid="{944DD57D-6054-446C-8A3C-0023E5B9F84C}"/>
+    <hyperlink ref="E37" r:id="rId46" xr:uid="{E243C969-D32B-42B8-8FEF-3E974F93FDE5}"/>
+    <hyperlink ref="E36" r:id="rId47" xr:uid="{000FD2BC-18E2-48A1-887F-40CEA0556CBF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId46"/>
+  <pageSetup orientation="portrait" r:id="rId48"/>
 </worksheet>
 </file>
--- a/doc/POPPy.xlsx
+++ b/doc/POPPy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oreil\Documents\GitHub\poppy\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49512DF8-C64E-4CCD-B8C0-25A8A4FD6A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A82CB6-F701-45EA-9588-880CDE1A8495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="636" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="388">
   <si>
     <t>Database</t>
   </si>
@@ -830,6 +830,318 @@
   </si>
   <si>
     <t>© World Health Organization 1998</t>
+  </si>
+  <si>
+    <t>Republic of Korea</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (Korean name, English name, Latin name, parts used, traditional uses, description, habitat, distribution, bio activities, chemical componenets, refferences)</t>
+  </si>
+  <si>
+    <t>Handbook of Ayurvedic Medicinal Plants</t>
+  </si>
+  <si>
+    <t>First pulished by CRC Press LLC © 1990  © 2001 by CRC Press LLC</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (latin name, family, vernacular names, habitat, morphological characteristics, parts used, aturvedic description, action and uses, chemical constituents, pharmalogical action, medicinal properties and uses, doses)</t>
+  </si>
+  <si>
+    <t>Kapoor, L.D. (2001). Handbook of Ayurvedic Medicinal Plants: Herbal Reference Library (1st ed.). Routledge. https://doi.org/10.1201/9780203719473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medicinal Plants in the South Pacific </t>
+  </si>
+  <si>
+    <t>World Health Organization. Regional Office for the Western Pacific (1998). Medicinal plants in the South Pacific : information on 102 commonly used medicinal plants in the South Pacific. WHO Regional Office for the Western Pacific. http://iris.wpro.who.int/handle/10665.1/6738</t>
+  </si>
+  <si>
+    <t>ISBN 92 9061 1189 © WorldHeallbOrganizalion 1998</t>
+  </si>
+  <si>
+    <t>Kinda- gives constituetns and biological activity of each plant</t>
+  </si>
+  <si>
+    <t>Kinda- gives the chemical constituents</t>
+  </si>
+  <si>
+    <t>Kinda- sometimes mentioned in medicinal properties and uses</t>
+  </si>
+  <si>
+    <t>Kinda- mentioned sometimes in traditional uses</t>
+  </si>
+  <si>
+    <t>South Pacific</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (latin name, local names, description, habitat, distribution, constituents, biological activity, traditional uses)</t>
+  </si>
+  <si>
+    <t>The Tropical Plant Database</t>
+  </si>
+  <si>
+    <t>© Copyrighted 2019 Rain-Tree Publishers All rights reserved.</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (family, genus, species, synonyms, common names, parts used, properties and actions, tribal and herbal medicine uses, plant chemicals, biological activities and clinical research, current practical uses, plant summary, worldwide ethnomedical uses, published research)</t>
+  </si>
+  <si>
+    <t>Wealth of the Rainforest, Pharmacy to the World, by Leslie Taylor, Copyrighted 1996 to present by Leslie Taylor, Milam County, Texas 77857. Online at http://www.rain-tree.com</t>
+  </si>
+  <si>
+    <t>You have to get written authorization from the author to use, transmit, or reproduce the database (There is educational exceptions but I'm not sure if this would count)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippine Medicinal Plants </t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Data Format</t>
+  </si>
+  <si>
+    <t>Still Available?</t>
+  </si>
+  <si>
+    <t>PubMed ID</t>
+  </si>
+  <si>
+    <t>Identifiers</t>
+  </si>
+  <si>
+    <t>Phytochemical- general</t>
+  </si>
+  <si>
+    <t>Biomedical- general</t>
+  </si>
+  <si>
+    <t>Online Database</t>
+  </si>
+  <si>
+    <t>No PubMed article</t>
+  </si>
+  <si>
+    <t>Plant taxonomy- medicinal</t>
+  </si>
+  <si>
+    <t>Plant taxonomy- general</t>
+  </si>
+  <si>
+    <t>http://bidd2.nus.edu.sg/CMAUP/</t>
+  </si>
+  <si>
+    <t>Journal Article</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.who.int/publications/i/item/9290611200 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://files.spiritmaji.com/books/diet-herbal-ayurveda-remedies/Handbook%20of%20Ayurvedic%20Medicinal%20-%20L.D.%20Kapoor.pdf </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://iris.who.int/items/a381e797-ac83-4601-a845-45890ef76413 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.rain-tree.com/plants.htm </t>
+  </si>
+  <si>
+    <t>Downloadable dataset, suplementary data table (apparently)</t>
+  </si>
+  <si>
+    <t>Downloadable links to pages with text of code information, downloads as H5 files</t>
+  </si>
+  <si>
+    <t>Dataset able to be downloaded but it is within each search "topic" not the whole database in one download. It is available in CSV and XLSX formats.</t>
+  </si>
+  <si>
+    <t>Downloadable links, some download as excel spreadsheets, some as CSV files</t>
+  </si>
+  <si>
+    <t>Downloadable PDF</t>
+  </si>
+  <si>
+    <t>Kinda- gives some constituents of the plant</t>
+  </si>
+  <si>
+    <t>Kinda- through the uses section</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (family, common names, scientific names, other vernacular names, general info, botany, distribution, constituents, properties, toxicity, parts used, uses, studies, availability)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Philippines </t>
+  </si>
+  <si>
+    <t>I couldn't find anywhere to download information and the copyright info page suggests that downloads were removed because people kept stealing the info</t>
+  </si>
+  <si>
+    <t>Just talks  about how info got stolen and how the author is mad about it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harindran, Jyoti. (2016). An illustrated compilation of Philippine medicinal plants by Dr Godofredo Stuart. 10.13140/RG.2.2.11918.36160. </t>
+  </si>
+  <si>
+    <t>Plant Species in the Folk medicine of Kit Mikayi Region, Western Kenya</t>
+  </si>
+  <si>
+    <t>Western Kenya</t>
+  </si>
+  <si>
+    <t>Provides info on different plants (plant name, uses, part used, family name)</t>
+  </si>
+  <si>
+    <t>© All content, imagery, and photos are copyrighted / Godofredo U. Stuart, Jr., MD • StuartXchange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://opensiuc.lib.siu.edu/cgi/viewcontent.cgi?article=1672&amp;context=ebl </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.stuartxchange.org/CompleteList.html </t>
+  </si>
+  <si>
+    <t>https://www.knapsackfamily.com/knapsack_core/top.php</t>
+  </si>
+  <si>
+    <t>KNApSAcK</t>
+  </si>
+  <si>
+    <t>© 2007 NARA INSTITUTE of SCIENCE and TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>Common names, formula, CAS RN, C_ID, InChIKey, InChICode, SMILES)</t>
+  </si>
+  <si>
+    <t>Yes, 24,776 species- includes animals, bacteria, fungi as well but it does specify which of these catagories an organism is</t>
+  </si>
+  <si>
+    <t>Yes, 63,735</t>
+  </si>
+  <si>
+    <t>Nakamura Y, Afendi FM, Parvin AK, Ono N, Tanaka K, Hirai Morita A, Sato T, Sugiura T, Altaf-Ul-Amin M, Kanaya S. KNApSAcK Metabolite Activity Database for retrieving the relationships between metabolites and biological activities. Plant Cell Physiol. 2014 Jan;55(1):e7. doi: 10.1093/pcp/pct176. Epub 2013 Nov 27. PMID: 24285751.</t>
+  </si>
+  <si>
+    <t>Binding DB</t>
+  </si>
+  <si>
+    <t>https://www.bindingdb.org/rwd/bind/index.jsp</t>
+  </si>
+  <si>
+    <t>Provides info on different compounds as well as the organisms they are found in, you can also search the organism name and get a list of the compounds present in that organism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Creativecommons attribution 3.0 lisence </t>
+  </si>
+  <si>
+    <t>Free to share and adapt but you must give appropriate credit</t>
+  </si>
+  <si>
+    <t>Kinda- gives FDA drugs with compound</t>
+  </si>
+  <si>
+    <t>Common name, SMILES, InChI</t>
+  </si>
+  <si>
+    <t>Able to download files in TSV or Sdfile formats</t>
+  </si>
+  <si>
+    <t>Provides info on different compounds (name, chemical structure pathways, chemical structure, data, targets, publications, special datasets)</t>
+  </si>
+  <si>
+    <t>Chen X, Liu M, Gilson MK. BindingDB: a web-accessible molecular recognition database. Comb Chem High Throughput Screen. 2001 Dec;4(8):719-25. doi: 10.2174/1386207013330670. PMID: 11812264.</t>
+  </si>
+  <si>
+    <t>PhytoHub</t>
+  </si>
+  <si>
+    <t>https://phytohub.eu/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provides info on food phytochemicals, known metabolites, and predicted metabolites </t>
+  </si>
+  <si>
+    <t>Kinda- some of the food sources are plants</t>
+  </si>
+  <si>
+    <t>PhytoHub ID, name, systematic name, synonyms, CAS number, chemical formula, IUPAC name, InChI Key, InChI identifier, SMILES</t>
+  </si>
+  <si>
+    <t>https://gcprohru.ac.in/wp-content/uploads/2020/06/Dictionary-of-Natural-Product.pdf</t>
+  </si>
+  <si>
+    <t>Dictionary of Natural Products on CD-ROM</t>
+  </si>
+  <si>
+    <t>Common name, IUPAC name, CAS registry number</t>
+  </si>
+  <si>
+    <t>Provides info on different compounds(images of their structure, nmes, chemical group info, types of compounds, reactions)</t>
+  </si>
+  <si>
+    <t>https://foodb.ca/</t>
+  </si>
+  <si>
+    <t>FooDB</t>
+  </si>
+  <si>
+    <t>Common name, primary ID, secondary accession sumbers, FooDB name, CAS number, synonyms, chemial formula, IUPAC name, InChI identifier, InChI key, isomeric SMILES</t>
+  </si>
+  <si>
+    <t>Provides info on different compounds( record info, chemical info, classification, ontology, physio chemical properties, spectra, external links, associated foods, biological effects and interactions, organoleptic properties, references) and plants( general info, clssification, taxonomy, external links, composition, references)</t>
+  </si>
+  <si>
+    <t>Free to share and adapt, but you must give credit and you can not use the material for commercial purposes</t>
+  </si>
+  <si>
+    <t>Naveja JJ, Rico-Hidalgo MP, Medina-Franco JL. Analysis of a large food chemical database: chemical space, diversity, and complexity. F1000Res. 2018 Jul 3;7:Chem Inf Sci-993. doi: 10.12688/f1000research.15440.2. PMID: 30135721; PMCID: PMC6081979.</t>
+  </si>
+  <si>
+    <t>Dataset able to be downloaded as CSV file, XML file, JSON file, MySQL dump file, as well as spectra downloads</t>
+  </si>
+  <si>
+    <t>The Human Metabolome Database (HMDB) </t>
+  </si>
+  <si>
+    <t>https://hmdb.ca/</t>
+  </si>
+  <si>
+    <t>Wishart DS, Guo AC, Oler E, et al., HMDB 5.0: the Human Metabolome Database for 2022. Nucleic Acids Res. 2022. Jan 7;50(D1):D622–31. 34986597 </t>
+  </si>
+  <si>
+    <t>Kinda- includes some metabolites from plants</t>
+  </si>
+  <si>
+    <t>Common name, HMBD ID, secondary accession numbers, synonyms, chemical formula, IUPAC name, traditional name, CAS registry number, SMILES, InChI identifier, InChI key</t>
+  </si>
+  <si>
+    <t>Kinda- in health effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provides info on different metabolites( identification, taxonomy, ontology, physical properties, spectra, biological properties, concentrations, links, refferences) </t>
+  </si>
+  <si>
+    <t>Data sets available to be downloaded as SDF files and XML files</t>
+  </si>
+  <si>
+    <t>https://www.genome.jp/kegg/</t>
+  </si>
+  <si>
+    <t>Provides info on different molecular interaction and reaction pathways. Also includes information on metabolism, gnetic information processing, environmental information processing, cellular processes, organismal systems, human diseases, and drug development</t>
+  </si>
+  <si>
+    <t>Kanehisa Laboratories</t>
+  </si>
+  <si>
+    <t>Includes a copyright permission request form to use the maps and figures in acedemic publications</t>
+  </si>
+  <si>
+    <t>KEGG: Kyoto Encyclopedia of Genes and Genomes</t>
+  </si>
+  <si>
+    <t>Kanehisa M, Goto S. KEGG: kyoto encyclopedia of genes and genomes. Nucleic Acids Res. 2000 Jan 1;28(1):27-30. doi: 10.1093/nar/28.1.27. PMID: 10592173; PMCID: PMC102409.</t>
   </si>
   <si>
     <r>
@@ -839,7 +1151,6 @@
       <rPr>
         <i/>
         <sz val="11"/>
-        <color rgb="FF222222"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -848,11 +1159,208 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF222222"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
       <t> 3, no. 1: 7. https://doi.org/10.3390/data3010007</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>ndian </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>M</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>edicinal </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>lants, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>P</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>hytochemistry </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>nd </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>T</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>herapeutics 2.0 (</t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>IMPPAT 2.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Whistler, W. A. (1990). ETHNOBOTANY OF THE COOK ISLANDS: THE PLANTS, THEIR MAORI NAMES, AND THEIR USES. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Allertonia</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(4), 347–424. http://www.jstor.org.proxy.library.upenn.edu/stable/23187400</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">World Health Organization Regional Office for the Western Pacific. (1998). </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Medicinal plants in the Republic of Korea : information on 150 commonly used medicinal plants</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>. World Health Organization, Regional Office for the Western Pacific.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Phanuel, Arwa S.; O., Nyunja R.; and C., Onyango J. (2010) "Plant Species in the Folk medicine of Kit Mikayi Region, Western Kenya," </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Ethnobotanical Leaflets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: Vol. 2010: Iss. 7, Article 13. Available at: https://opensiuc.lib.siu.edu/ebl/vol2010/iss7/13</t>
     </r>
   </si>
   <si>
@@ -863,7 +1371,6 @@
       <rPr>
         <i/>
         <sz val="11"/>
-        <color rgb="FF222222"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -872,7 +1379,6 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF222222"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -882,7 +1388,6 @@
       <rPr>
         <i/>
         <sz val="11"/>
-        <color rgb="FF222222"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
@@ -891,494 +1396,63 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FF222222"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
       </rPr>
-      <t> </t>
+      <t> 25, 1251–1255 (2007). https://doi.org/10.1038/nbt1346</t>
     </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF222222"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>25</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF222222"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>, 1251–1255 (2007). https://doi.org/10.1038/nbt1346</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>I</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>ndian </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>M</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>edicinal </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>lants, </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>P</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>hytochemistry </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>A</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>nd </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>T</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>herapeutics 2.0 (</t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>IMPPAT 2.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF212529"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Whistler, W. A. (1990). ETHNOBOTANY OF THE COOK ISLANDS: THE PLANTS, THEIR MAORI NAMES, AND THEIR USES. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Allertonia</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(4), 347–424. http://www.jstor.org.proxy.library.upenn.edu/stable/23187400</t>
-    </r>
-  </si>
-  <si>
-    <t>Republic of Korea</t>
-  </si>
-  <si>
-    <t>Provides info on different plants (Korean name, English name, Latin name, parts used, traditional uses, description, habitat, distribution, bio activities, chemical componenets, refferences)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">World Health Organization Regional Office for the Western Pacific. (1998). </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Medicinal plants in the Republic of Korea : information on 150 commonly used medicinal plants</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>. World Health Organization, Regional Office for the Western Pacific.</t>
-    </r>
-  </si>
-  <si>
-    <t>Handbook of Ayurvedic Medicinal Plants</t>
-  </si>
-  <si>
-    <t>First pulished by CRC Press LLC © 1990  © 2001 by CRC Press LLC</t>
-  </si>
-  <si>
-    <t>Provides info on different plants (latin name, family, vernacular names, habitat, morphological characteristics, parts used, aturvedic description, action and uses, chemical constituents, pharmalogical action, medicinal properties and uses, doses)</t>
-  </si>
-  <si>
-    <t>Kapoor, L.D. (2001). Handbook of Ayurvedic Medicinal Plants: Herbal Reference Library (1st ed.). Routledge. https://doi.org/10.1201/9780203719473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medicinal Plants in the South Pacific </t>
-  </si>
-  <si>
-    <t>World Health Organization. Regional Office for the Western Pacific (1998). Medicinal plants in the South Pacific : information on 102 commonly used medicinal plants in the South Pacific. WHO Regional Office for the Western Pacific. http://iris.wpro.who.int/handle/10665.1/6738</t>
-  </si>
-  <si>
-    <t>ISBN 92 9061 1189 © WorldHeallbOrganizalion 1998</t>
-  </si>
-  <si>
-    <t>Kinda- gives constituetns and biological activity of each plant</t>
-  </si>
-  <si>
-    <t>Kinda- gives the chemical constituents</t>
-  </si>
-  <si>
-    <t>Kinda- sometimes mentioned in medicinal properties and uses</t>
-  </si>
-  <si>
-    <t>Kinda- mentioned sometimes in traditional uses</t>
-  </si>
-  <si>
-    <t>South Pacific</t>
-  </si>
-  <si>
-    <t>Provides info on different plants (latin name, local names, description, habitat, distribution, constituents, biological activity, traditional uses)</t>
-  </si>
-  <si>
-    <t>The Tropical Plant Database</t>
-  </si>
-  <si>
-    <t>© Copyrighted 2019 Rain-Tree Publishers All rights reserved.</t>
-  </si>
-  <si>
-    <t>Provides info on different plants (family, genus, species, synonyms, common names, parts used, properties and actions, tribal and herbal medicine uses, plant chemicals, biological activities and clinical research, current practical uses, plant summary, worldwide ethnomedical uses, published research)</t>
-  </si>
-  <si>
-    <t>Wealth of the Rainforest, Pharmacy to the World, by Leslie Taylor, Copyrighted 1996 to present by Leslie Taylor, Milam County, Texas 77857. Online at http://www.rain-tree.com</t>
-  </si>
-  <si>
-    <t>You have to get written authorization from the author to use, transmit, or reproduce the database (There is educational exceptions but I'm not sure if this would count)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philippine Medicinal Plants </t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Data Format</t>
-  </si>
-  <si>
-    <t>Still Available?</t>
-  </si>
-  <si>
-    <t>PubMed ID</t>
-  </si>
-  <si>
-    <t>Identifiers</t>
-  </si>
-  <si>
-    <t>Phytochemical- general</t>
-  </si>
-  <si>
-    <t>Biomedical- general</t>
-  </si>
-  <si>
-    <t>Online Database</t>
-  </si>
-  <si>
-    <t>No PubMed article</t>
-  </si>
-  <si>
-    <t>Plant taxonomy- medicinal</t>
-  </si>
-  <si>
-    <t>Plant taxonomy- general</t>
-  </si>
-  <si>
-    <t>http://bidd2.nus.edu.sg/CMAUP/</t>
-  </si>
-  <si>
-    <t>Journal Article</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.who.int/publications/i/item/9290611200 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://files.spiritmaji.com/books/diet-herbal-ayurveda-remedies/Handbook%20of%20Ayurvedic%20Medicinal%20-%20L.D.%20Kapoor.pdf </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://iris.who.int/items/a381e797-ac83-4601-a845-45890ef76413 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.rain-tree.com/plants.htm </t>
-  </si>
-  <si>
-    <t>Downloadable dataset, suplementary data table (apparently)</t>
-  </si>
-  <si>
-    <t>Downloadable links to pages with text of code information, downloads as H5 files</t>
-  </si>
-  <si>
-    <t>Dataset able to be downloaded but it is within each search "topic" not the whole database in one download. It is available in CSV and XLSX formats.</t>
-  </si>
-  <si>
-    <t>Downloadable links, some download as excel spreadsheets, some as CSV files</t>
-  </si>
-  <si>
-    <t>Downloadable PDF</t>
-  </si>
-  <si>
-    <t>Kinda- gives some constituents of the plant</t>
-  </si>
-  <si>
-    <t>Kinda- through the uses section</t>
-  </si>
-  <si>
-    <t>Provides info on different plants (family, common names, scientific names, other vernacular names, general info, botany, distribution, constituents, properties, toxicity, parts used, uses, studies, availability)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Philippines </t>
-  </si>
-  <si>
-    <t>I couldn't find anywhere to download information and the copyright info page suggests that downloads were removed because people kept stealing the info</t>
-  </si>
-  <si>
-    <t>Just talks  about how info got stolen and how the author is mad about it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harindran, Jyoti. (2016). An illustrated compilation of Philippine medicinal plants by Dr Godofredo Stuart. 10.13140/RG.2.2.11918.36160. </t>
-  </si>
-  <si>
-    <t>Plant Species in the Folk medicine of Kit Mikayi Region, Western Kenya</t>
-  </si>
-  <si>
-    <t>Western Kenya</t>
-  </si>
-  <si>
-    <r>
-      <t>Phanuel, Arwa S.; O., Nyunja R.; and C., Onyango J. (2010) "Plant Species in the Folk medicine of Kit Mikayi Region, Western Kenya," </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Ethnobotanical Leaflets</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>: Vol. 2010: Iss. 7, Article 13. Available at: https://opensiuc.lib.siu.edu/ebl/vol2010/iss7/13</t>
-    </r>
-  </si>
-  <si>
-    <t>Provides info on different plants (plant name, uses, part used, family name)</t>
-  </si>
-  <si>
-    <t>© All content, imagery, and photos are copyrighted / Godofredo U. Stuart, Jr., MD • StuartXchange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://opensiuc.lib.siu.edu/cgi/viewcontent.cgi?article=1672&amp;context=ebl </t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.stuartxchange.org/CompleteList.html </t>
-  </si>
-  <si>
-    <t>https://www.knapsackfamily.com/knapsack_core/top.php</t>
-  </si>
-  <si>
-    <t>KNApSAcK</t>
-  </si>
-  <si>
-    <t>© 2007 NARA INSTITUTE of SCIENCE and TECHNOLOGY</t>
-  </si>
-  <si>
-    <t>Common names, formula, CAS RN, C_ID, InChIKey, InChICode, SMILES)</t>
-  </si>
-  <si>
-    <t>Yes, 24,776 species- includes animals, bacteria, fungi as well but it does specify which of these catagories an organism is</t>
-  </si>
-  <si>
-    <t>Yes, 63,735</t>
-  </si>
-  <si>
-    <t>Nakamura Y, Afendi FM, Parvin AK, Ono N, Tanaka K, Hirai Morita A, Sato T, Sugiura T, Altaf-Ul-Amin M, Kanaya S. KNApSAcK Metabolite Activity Database for retrieving the relationships between metabolites and biological activities. Plant Cell Physiol. 2014 Jan;55(1):e7. doi: 10.1093/pcp/pct176. Epub 2013 Nov 27. PMID: 24285751.</t>
-  </si>
-  <si>
-    <t>Binding DB</t>
-  </si>
-  <si>
-    <t>https://www.bindingdb.org/rwd/bind/index.jsp</t>
-  </si>
-  <si>
-    <t>Provides info on different compounds as well as the organisms they are found in, you can also search the organism name and get a list of the compounds present in that organism</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Creativecommons attribution 3.0 lisence </t>
-  </si>
-  <si>
-    <t>Free to share and adapt but you must give appropriate credit</t>
-  </si>
-  <si>
-    <t>Kinda- gives FDA drugs with compound</t>
-  </si>
-  <si>
-    <t>Common name, SMILES, InChI</t>
-  </si>
-  <si>
-    <t>Able to download files in TSV or Sdfile formats</t>
-  </si>
-  <si>
-    <t>Provides info on different compounds (name, chemical structure pathways, chemical structure, data, targets, publications, special datasets)</t>
-  </si>
-  <si>
-    <t>Chen X, Liu M, Gilson MK. BindingDB: a web-accessible molecular recognition database. Comb Chem High Throughput Screen. 2001 Dec;4(8):719-25. doi: 10.2174/1386207013330670. PMID: 11812264.</t>
-  </si>
-  <si>
-    <t>PhytoHub</t>
-  </si>
-  <si>
-    <t>https://phytohub.eu/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provides info on food phytochemicals, known metabolites, and predicted metabolites </t>
-  </si>
-  <si>
-    <t>Kinda- some of the food sources are plants</t>
-  </si>
-  <si>
-    <t>PhytoHub ID, name, systematic name, synonyms, CAS number, chemical formula, IUPAC name, InChI Key, InChI identifier, SMILES</t>
+  </si>
+  <si>
+    <t>Plant Metabolic Network (PMN)</t>
+  </si>
+  <si>
+    <t>https://plantcyc.org/</t>
+  </si>
+  <si>
+    <t>Contains a license agreement form and says that the license is freely available to everyone including commercial users. Fee to modify and redistribute with appropriate credit given</t>
+  </si>
+  <si>
+    <t>Available to download BLAST sets, SAVI validation sets, and tab-delimited text files</t>
+  </si>
+  <si>
+    <t>Provides info on metabolic pathways, catalytic enzymes, compounds, and genes from different plant species</t>
+  </si>
+  <si>
+    <t>Varries within different resources</t>
+  </si>
+  <si>
+    <t>Hawkins C, Xue B, Yasmin F, Wyatt G, Zerbe P, Rhee SY. Plant Metabolic Network 16: expansion of underrepresented plant groups and experimentally supported enzyme data. Nucleic Acids Res. 2025 Jan 6;53(D1):D1606-D1613. doi: 10.1093/nar/gkae991. Erratum in: Nucleic Acids Res. 2025 Jan 6;53(D1):D1726. doi: 10.1093/nar/gkae1231. PMID: 39558185; PMCID: PMC11701740.</t>
+  </si>
+  <si>
+    <t>The Natural Products Atlas</t>
+  </si>
+  <si>
+    <t>https://www.npatlas.org/</t>
+  </si>
+  <si>
+    <t>Creative Commons Attribution Noncommercial 4.0 International License</t>
+  </si>
+  <si>
+    <t>Free to share and adapt, but must give appropriate credit and the material may not be used for commercial purposes</t>
+  </si>
+  <si>
+    <t>Available to donwload TSV file, Excel file, JSON file, SDF file, and grphML files</t>
+  </si>
+  <si>
+    <t>NPAID, cluster ID, name, formula, InChIKey, InChI, SMILES</t>
+  </si>
+  <si>
+    <t>Provides info on different microbially derived natural products such as their structure, origin, domain, phylum, class, order, family, and genus</t>
+  </si>
+  <si>
+    <t>van Santen JA, Poynton EF, Iskakova D, McMann E, Alsup TA, Clark TN, Fergusson CH, Fewer DP, Hughes AH, McCadden CA, Parra J, Soldatou S, Rudolf JD, Janssen EM, Duncan KR, Linington RG. The Natural Products Atlas 2.0: a database of microbially-derived natural products. Nucleic Acids Res. 2022 Jan 7;50(D1):D1317-D1323. doi: 10.1093/nar/gkab941. PMID: 34718710; PMCID: PMC8728154.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1403,91 +1477,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF2A2A2A"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF252525"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF262626"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF212529"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF212529"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF2E414F"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1503,8 +1493,20 @@
       <family val="1"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF202020"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF232B2B"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1564,75 +1566,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1676,130 +1661,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -2131,79 +1992,79 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="7"/>
-    <col min="2" max="2" width="14.7265625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.54296875" style="7" customWidth="1"/>
-    <col min="5" max="8" width="32.26953125" style="7" customWidth="1"/>
-    <col min="9" max="11" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="21.7265625" style="7" customWidth="1"/>
-    <col min="14" max="16" width="36.54296875" style="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="22.7265625" style="7" customWidth="1"/>
-    <col min="18" max="18" width="34.1796875" style="7" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.26953125" style="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.1796875" style="7"/>
+    <col min="1" max="1" width="9.1796875" style="3"/>
+    <col min="2" max="2" width="14.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="36.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.54296875" style="3" customWidth="1"/>
+    <col min="5" max="8" width="32.26953125" style="3" customWidth="1"/>
+    <col min="9" max="11" width="36.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="21.7265625" style="3" customWidth="1"/>
+    <col min="14" max="16" width="36.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="22.7265625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="34.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2211,49 +2072,49 @@
       <c r="A2" s="7">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E2" s="4" t="s">
+      <c r="D2" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="10">
         <v>39588778</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="4" t="s">
         <v>17</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="4" t="s">
         <v>21</v>
       </c>
       <c r="O2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="4" t="s">
         <v>23</v>
       </c>
       <c r="Q2" s="7" t="s">
@@ -2270,40 +2131,40 @@
       <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E3" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="10">
         <v>17932057</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="4" t="s">
         <v>30</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="4" t="s">
         <v>33</v>
       </c>
       <c r="N3" s="7" t="s">
@@ -2312,7 +2173,7 @@
       <c r="O3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="4" t="s">
         <v>35</v>
       </c>
       <c r="Q3" s="7" t="s">
@@ -2329,37 +2190,38 @@
       <c r="A4" s="7">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C4" s="8" t="s">
+      <c r="B4" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="10">
         <v>39558177</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="4" t="s">
         <v>39</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="K4" s="7"/>
+      <c r="L4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="4" t="s">
         <v>42</v>
       </c>
       <c r="N4" s="7" t="s">
@@ -2368,7 +2230,7 @@
       <c r="O4" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="P4" s="6" t="s">
+      <c r="P4" s="4" t="s">
         <v>45</v>
       </c>
       <c r="Q4" s="7" t="s">
@@ -2377,42 +2239,43 @@
       <c r="R4" s="7" t="s">
         <v>47</v>
       </c>
+      <c r="S4" s="7"/>
     </row>
     <row r="5" spans="1:19" ht="168" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="10">
         <v>14681407</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="4" t="s">
         <v>54</v>
       </c>
       <c r="M5" s="7" t="s">
@@ -2421,7 +2284,7 @@
       <c r="N5" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="4" t="s">
         <v>55</v>
       </c>
       <c r="P5" s="7" t="s">
@@ -2441,38 +2304,38 @@
       <c r="A6" s="7">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="I6" s="6" t="s">
+      <c r="F6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>307</v>
+      <c r="L6" s="4" t="s">
+        <v>302</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>33</v>
@@ -2483,7 +2346,7 @@
       <c r="O6" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="4" t="s">
         <v>63</v>
       </c>
       <c r="Q6" s="7" t="s">
@@ -2500,37 +2363,37 @@
       <c r="A7" s="7">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="B7" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="F7" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="10">
         <v>32761142</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="4" t="s">
         <v>69</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="4" t="s">
         <v>71</v>
       </c>
       <c r="M7" s="7" t="s">
@@ -2539,7 +2402,7 @@
       <c r="N7" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="O7" s="4" t="s">
         <v>73</v>
       </c>
       <c r="P7" s="7" t="s">
@@ -2559,34 +2422,35 @@
       <c r="A8" s="7">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="H8" s="22">
+      <c r="F8" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="H8" s="10">
         <v>17989687</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="K8" s="7"/>
+      <c r="L8" s="4" t="s">
         <v>78</v>
       </c>
       <c r="M8" s="7" t="s">
@@ -2595,7 +2459,7 @@
       <c r="N8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="4" t="s">
         <v>80</v>
       </c>
       <c r="P8" s="7" t="s">
@@ -2615,38 +2479,38 @@
       <c r="A9" s="7">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>296</v>
+      <c r="B9" s="4" t="s">
+        <v>291</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>83</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E9" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="10">
         <v>39552041</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="L9" s="6" t="s">
-        <v>308</v>
+      <c r="L9" s="4" t="s">
+        <v>303</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>33</v>
@@ -2654,7 +2518,7 @@
       <c r="N9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="O9" s="4" t="s">
         <v>89</v>
       </c>
       <c r="P9" s="7" t="s">
@@ -2674,40 +2538,40 @@
       <c r="A10" s="7">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>296</v>
+      <c r="B10" s="4" t="s">
+        <v>291</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>90</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E10" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="10">
         <v>32117874</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="4" t="s">
         <v>97</v>
       </c>
       <c r="N10" s="7" t="s">
@@ -2716,10 +2580,10 @@
       <c r="O10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="P10" s="6" t="s">
+      <c r="P10" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="Q10" s="4" t="s">
         <v>99</v>
       </c>
       <c r="R10" s="7" t="s">
@@ -2733,90 +2597,96 @@
       <c r="A11" s="7">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="B11" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="D11" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="10">
         <v>30357356</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="4" t="s">
         <v>102</v>
       </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
       <c r="N11" s="7" t="s">
         <v>33</v>
       </c>
       <c r="O11" s="7" t="s">
         <v>103</v>
       </c>
+      <c r="P11" s="7"/>
       <c r="Q11" s="7" t="s">
         <v>33</v>
       </c>
       <c r="R11" s="7" t="s">
         <v>104</v>
       </c>
+      <c r="S11" s="7"/>
     </row>
     <row r="12" spans="1:19" ht="140" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>295</v>
+      <c r="B12" s="4" t="s">
+        <v>290</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>105</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E12" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <v>35616633</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="4" t="s">
         <v>111</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="4" t="s">
         <v>112</v>
       </c>
       <c r="O12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="P12" s="6" t="s">
+      <c r="P12" s="4" t="s">
         <v>113</v>
       </c>
       <c r="Q12" s="7" t="s">
@@ -2833,78 +2703,81 @@
       <c r="A13" s="7">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="B13" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="D13" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="22">
+      <c r="H13" s="10">
         <v>41243954</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="4" t="s">
         <v>118</v>
       </c>
       <c r="M13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="4" t="s">
         <v>119</v>
       </c>
       <c r="O13" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="P13" s="6" t="s">
+      <c r="P13" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="Q13" s="6" t="s">
+      <c r="Q13" s="4" t="s">
         <v>122</v>
       </c>
       <c r="R13" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="S13" s="7"/>
     </row>
     <row r="14" spans="1:19" ht="103" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B14" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="D14" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="10" t="s">
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="H14" s="10" t="s">
-        <v>298</v>
-      </c>
-      <c r="I14" s="6" t="s">
+      <c r="H14" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>126</v>
       </c>
       <c r="J14" s="7" t="s">
@@ -2913,8 +2786,8 @@
       <c r="K14" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="L14" s="6" t="s">
-        <v>309</v>
+      <c r="L14" s="4" t="s">
+        <v>304</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>33</v>
@@ -2942,38 +2815,38 @@
       <c r="A15" s="7">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>300</v>
+      <c r="B15" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>131</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E15" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="11" t="s">
+      <c r="F15" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="H15" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="I15" s="6" t="s">
+      <c r="H15" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="J15" s="6" t="s">
+      <c r="J15" s="4" t="s">
         <v>135</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="L15" s="6" t="s">
-        <v>310</v>
+      <c r="L15" s="4" t="s">
+        <v>305</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>33</v>
@@ -2993,33 +2866,34 @@
       <c r="R15" s="7" t="s">
         <v>138</v>
       </c>
+      <c r="S15" s="7"/>
     </row>
     <row r="16" spans="1:19" ht="126" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="B16" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="D16" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="F16" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="10">
         <v>24735618</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="4" t="s">
         <v>142</v>
       </c>
       <c r="J16" s="7" t="s">
@@ -3028,7 +2902,7 @@
       <c r="K16" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="4" t="s">
         <v>145</v>
       </c>
       <c r="M16" s="7" t="s">
@@ -3040,7 +2914,7 @@
       <c r="O16" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="P16" s="4" t="s">
         <v>148</v>
       </c>
       <c r="Q16" s="7" t="s">
@@ -3057,37 +2931,37 @@
       <c r="A17" s="7">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="B17" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="14" t="s">
+      <c r="F17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="10">
         <v>36910986</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="L17" s="6" t="s">
+      <c r="L17" s="4" t="s">
         <v>154</v>
       </c>
       <c r="M17" s="7" t="s">
@@ -3099,51 +2973,52 @@
       <c r="O17" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="P17" s="6" t="s">
+      <c r="P17" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="Q17" s="4" t="s">
         <v>158</v>
       </c>
       <c r="R17" s="7" t="s">
         <v>159</v>
       </c>
+      <c r="S17" s="7"/>
     </row>
     <row r="18" spans="1:19" ht="126" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>296</v>
+      <c r="B18" s="4" t="s">
+        <v>291</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>160</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E18" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E18" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="F18" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="10">
         <v>39558165</v>
       </c>
-      <c r="I18" s="6" t="s">
+      <c r="I18" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J18" s="6" t="s">
+      <c r="J18" s="4" t="s">
         <v>69</v>
       </c>
       <c r="K18" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="4" t="s">
         <v>164</v>
       </c>
       <c r="M18" s="7" t="s">
@@ -3155,48 +3030,50 @@
       <c r="O18" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="P18" s="6" t="s">
+      <c r="P18" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="Q18" s="6" t="s">
+      <c r="Q18" s="4" t="s">
         <v>167</v>
       </c>
       <c r="R18" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="S18" s="7"/>
     </row>
     <row r="19" spans="1:19" ht="140" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>296</v>
+      <c r="B19" s="4" t="s">
+        <v>291</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>168</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E19" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E19" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="F19" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G19" s="16" t="s">
+      <c r="F19" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G19" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="10">
         <v>41217946</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="J19" s="17" t="s">
+      <c r="J19" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L19" s="6" t="s">
+      <c r="K19" s="7"/>
+      <c r="L19" s="4" t="s">
         <v>173</v>
       </c>
       <c r="M19" s="7" t="s">
@@ -3208,7 +3085,7 @@
       <c r="O19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="P19" s="4" t="s">
         <v>174</v>
       </c>
       <c r="Q19" s="7" t="s">
@@ -3225,38 +3102,38 @@
       <c r="A20" s="7">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C20" s="17" t="s">
+      <c r="B20" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" s="15" t="s">
+      <c r="D20" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E20" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="F20" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="H20" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I20" s="6" t="s">
+      <c r="H20" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="J20" s="17" t="s">
+      <c r="J20" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="16" t="s">
         <v>179</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>33</v>
@@ -3276,43 +3153,44 @@
       <c r="R20" s="7" t="s">
         <v>180</v>
       </c>
+      <c r="S20" s="7"/>
     </row>
     <row r="21" spans="1:19" ht="98" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="B21" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>302</v>
-      </c>
-      <c r="E21" s="15" t="s">
+      <c r="D21" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E21" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="F21" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="H21" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I21" s="6" t="s">
+      <c r="H21" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="J21" s="17" t="s">
+      <c r="J21" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K21" s="15" t="s">
         <v>185</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>33</v>
@@ -3340,38 +3218,38 @@
       <c r="A22" s="7">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>299</v>
+      <c r="B22" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>186</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E22" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E22" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I22" s="6" t="s">
+      <c r="H22" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="J22" s="17" t="s">
+      <c r="J22" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K22" s="15" t="s">
         <v>190</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>33</v>
@@ -3399,38 +3277,38 @@
       <c r="A23" s="7">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>299</v>
+      <c r="B23" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>192</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E23" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E23" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="F23" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G23" s="6" t="s">
+      <c r="F23" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I23" s="6" t="s">
+      <c r="H23" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="J23" s="17" t="s">
+      <c r="J23" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K23" s="15" t="s">
         <v>196</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>33</v>
@@ -3458,38 +3336,38 @@
       <c r="A24" s="7">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>299</v>
+      <c r="B24" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>198</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E24" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E24" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G24" s="6" t="s">
+      <c r="F24" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I24" s="6" t="s">
+      <c r="H24" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J24" s="17" t="s">
+      <c r="J24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="K24" s="20" t="s">
+      <c r="K24" s="16" t="s">
         <v>202</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>33</v>
@@ -3509,43 +3387,44 @@
       <c r="R24" s="7" t="s">
         <v>203</v>
       </c>
+      <c r="S24" s="7"/>
     </row>
     <row r="25" spans="1:19" ht="98" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C25" s="17" t="s">
+      <c r="B25" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D25" s="17" t="s">
-        <v>302</v>
-      </c>
-      <c r="E25" s="15" t="s">
+      <c r="D25" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="E25" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="F25" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I25" s="6" t="s">
+      <c r="F25" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="K25" s="20" t="s">
+      <c r="K25" s="16" t="s">
         <v>202</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>33</v>
@@ -3559,42 +3438,45 @@
       <c r="P25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="Q25" s="6" t="s">
+      <c r="Q25" s="4" t="s">
         <v>208</v>
       </c>
       <c r="R25" s="7" t="s">
         <v>209</v>
       </c>
+      <c r="S25" s="7"/>
     </row>
     <row r="26" spans="1:19" ht="84" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>300</v>
+      <c r="B26" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>210</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E26" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E26" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="F26" s="15" t="s">
-        <v>33</v>
-      </c>
+      <c r="F26" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="7"/>
       <c r="H26" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I26" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="L26" s="6" t="s">
+      <c r="K26" s="7"/>
+      <c r="L26" s="4" t="s">
         <v>214</v>
       </c>
       <c r="M26" s="7" t="s">
@@ -3609,7 +3491,7 @@
       <c r="P26" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="Q26" s="6" t="s">
+      <c r="Q26" s="4" t="s">
         <v>215</v>
       </c>
       <c r="R26" s="7" t="s">
@@ -3623,8 +3505,8 @@
       <c r="A27" s="7">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>299</v>
+      <c r="B27" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>217</v>
@@ -3632,25 +3514,26 @@
       <c r="D27" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="F27" s="15" t="s">
-        <v>33</v>
-      </c>
+      <c r="F27" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="7"/>
       <c r="H27" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I27" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="K27" s="6" t="s">
+      <c r="K27" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="L27" s="6" t="s">
+      <c r="L27" s="4" t="s">
         <v>223</v>
       </c>
       <c r="M27" s="7" t="s">
@@ -3659,13 +3542,13 @@
       <c r="N27" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="O27" s="6" t="s">
+      <c r="O27" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="P27" s="6" t="s">
+      <c r="P27" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="Q27" s="6" t="s">
+      <c r="Q27" s="4" t="s">
         <v>226</v>
       </c>
       <c r="R27" s="7" t="s">
@@ -3679,37 +3562,37 @@
       <c r="A28" s="7">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>300</v>
+      <c r="B28" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>228</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E28" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E28" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="F28" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="18" t="s">
+      <c r="F28" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="H28" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="I28" s="6" t="s">
+      <c r="H28" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="J28" s="6" t="s">
+      <c r="J28" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="L28" s="6" t="s">
+      <c r="L28" s="4" t="s">
         <v>234</v>
       </c>
       <c r="M28" s="7" t="s">
@@ -3724,7 +3607,7 @@
       <c r="P28" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="Q28" s="6" t="s">
+      <c r="Q28" s="4" t="s">
         <v>236</v>
       </c>
       <c r="R28" s="7" t="s">
@@ -3738,37 +3621,37 @@
       <c r="A29" s="7">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="B29" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="14" t="s">
         <v>239</v>
       </c>
-      <c r="F29" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="6" t="s">
+      <c r="F29" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I29" s="6" t="s">
+      <c r="H29" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I29" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="J29" s="6" t="s">
+      <c r="J29" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="L29" s="6" t="s">
+      <c r="L29" s="4" t="s">
         <v>244</v>
       </c>
       <c r="M29" s="7" t="s">
@@ -3777,13 +3660,13 @@
       <c r="N29" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="O29" s="6" t="s">
+      <c r="O29" s="4" t="s">
         <v>245</v>
       </c>
       <c r="P29" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="Q29" s="6" t="s">
+      <c r="Q29" s="4" t="s">
         <v>247</v>
       </c>
       <c r="R29" s="7" t="s">
@@ -3797,8 +3680,8 @@
       <c r="A30" s="7">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>299</v>
+      <c r="B30" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>248</v>
@@ -3806,25 +3689,26 @@
       <c r="D30" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="F30" s="15" t="s">
-        <v>33</v>
-      </c>
+      <c r="F30" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G30" s="7"/>
       <c r="H30" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I30" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I30" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="L30" s="6" t="s">
+      <c r="L30" s="4" t="s">
         <v>244</v>
       </c>
       <c r="M30" s="7" t="s">
@@ -3833,13 +3717,13 @@
       <c r="N30" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="O30" s="6" t="s">
+      <c r="O30" s="4" t="s">
         <v>253</v>
       </c>
       <c r="P30" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="Q30" s="6" t="s">
+      <c r="Q30" s="4" t="s">
         <v>254</v>
       </c>
       <c r="R30" s="7" t="s">
@@ -3853,30 +3737,33 @@
       <c r="A31" s="7">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>300</v>
+      <c r="B31" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>255</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E31" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E31" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="F31" s="15" t="s">
-        <v>33</v>
-      </c>
+      <c r="F31" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G31" s="7"/>
       <c r="H31" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I31" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="K31" s="19" t="s">
+      <c r="J31" s="7"/>
+      <c r="K31" s="7" t="s">
         <v>258</v>
       </c>
+      <c r="L31" s="7"/>
       <c r="M31" s="7" t="s">
         <v>259</v>
       </c>
@@ -3903,8 +3790,8 @@
       <c r="A32" s="7">
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>299</v>
+      <c r="B32" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>261</v>
@@ -3912,25 +3799,26 @@
       <c r="D32" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E32" s="15" t="s">
-        <v>303</v>
+      <c r="E32" s="14" t="s">
+        <v>298</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="I32" s="21" t="s">
-        <v>268</v>
-      </c>
+      <c r="G32" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I32" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="J32" s="7"/>
       <c r="K32" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="L32" s="6" t="s">
+      <c r="L32" s="4" t="s">
         <v>244</v>
       </c>
       <c r="M32" s="7" t="s">
@@ -3949,7 +3837,7 @@
         <v>24</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="S32" s="7">
         <v>1998</v>
@@ -3959,50 +3847,51 @@
       <c r="A33" s="7">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>299</v>
+      <c r="B33" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E33" s="15" t="s">
-        <v>304</v>
+      <c r="E33" s="14" t="s">
+        <v>299</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="G33" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="J33" s="7"/>
+      <c r="K33" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O33" s="7" t="s">
         <v>273</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="N33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="O33" s="7" t="s">
-        <v>278</v>
       </c>
       <c r="P33" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="Q33" s="6" t="s">
-        <v>279</v>
+      <c r="Q33" s="4" t="s">
+        <v>274</v>
       </c>
       <c r="R33" s="7" t="s">
         <v>159</v>
@@ -4015,34 +3904,35 @@
       <c r="A34" s="7">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>299</v>
+      <c r="B34" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="E34" s="15" t="s">
-        <v>305</v>
+      <c r="E34" s="14" t="s">
+        <v>300</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G34" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="H34" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="L34" s="6" t="s">
+      <c r="G34" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="H34" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="J34" s="7"/>
+      <c r="K34" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>223</v>
       </c>
       <c r="M34" s="7" t="s">
@@ -4051,17 +3941,17 @@
       <c r="N34" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="O34" s="6" t="s">
-        <v>277</v>
+      <c r="O34" s="4" t="s">
+        <v>272</v>
       </c>
       <c r="P34" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="Q34" s="6" t="s">
-        <v>280</v>
+      <c r="Q34" s="4" t="s">
+        <v>275</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="S34" s="7">
         <v>1998</v>
@@ -4071,37 +3961,37 @@
       <c r="A35" s="7">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>300</v>
+      <c r="B35" s="4" t="s">
+        <v>295</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E35" s="15" t="s">
-        <v>306</v>
+        <v>292</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>301</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G35" s="17" t="s">
-        <v>286</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>298</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>287</v>
-      </c>
-      <c r="K35" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="L35" s="6" t="s">
+      <c r="G35" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>234</v>
       </c>
       <c r="M35" s="7" t="s">
@@ -4130,38 +4020,38 @@
       <c r="A36" s="7">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>299</v>
+      <c r="B36" s="4" t="s">
+        <v>294</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E36" s="15" t="s">
-        <v>325</v>
+        <v>292</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>319</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="6" t="s">
-        <v>318</v>
+      <c r="G36" s="4" t="s">
+        <v>313</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="J36" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="K36" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>316</v>
+      <c r="L36" s="4" t="s">
+        <v>311</v>
       </c>
       <c r="M36" s="7" t="s">
         <v>33</v>
@@ -4170,16 +4060,16 @@
         <v>33</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="P36" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="Q36" s="6" t="s">
-        <v>313</v>
+      <c r="Q36" s="4" t="s">
+        <v>308</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="S36" s="7">
         <v>2025</v>
@@ -4189,33 +4079,34 @@
       <c r="A37" s="7">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>319</v>
+      <c r="B37" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>314</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="E37" s="15" t="s">
-        <v>324</v>
+        <v>297</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>318</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G37" s="17" t="s">
-        <v>321</v>
+      <c r="G37" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="I37" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="J37" s="21"/>
+        <v>293</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="J37" s="17"/>
+      <c r="K37" s="7"/>
       <c r="L37" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="M37" s="7" t="s">
         <v>33</v>
@@ -4233,51 +4124,54 @@
         <v>33</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>320</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="S37" s="7"/>
     </row>
     <row r="38" spans="1:19" ht="140" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>295</v>
+      <c r="B38" s="4" t="s">
+        <v>290</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E38" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G38" s="4" t="s">
         <v>326</v>
       </c>
-      <c r="F38" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G38" s="24" t="s">
-        <v>332</v>
-      </c>
-      <c r="H38" s="22">
+      <c r="H38" s="10">
         <v>24285751</v>
       </c>
-      <c r="I38" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="K38" s="25" t="s">
-        <v>328</v>
-      </c>
+      <c r="I38" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="J38" s="7"/>
+      <c r="K38" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="L38" s="7"/>
       <c r="M38" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N38" s="6" t="s">
-        <v>330</v>
+      <c r="N38" s="4" t="s">
+        <v>324</v>
       </c>
       <c r="O38" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="P38" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>323</v>
       </c>
       <c r="Q38" s="7" t="s">
         <v>24</v>
@@ -4293,94 +4187,444 @@
       <c r="A39" s="7">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>296</v>
+      <c r="B39" s="4" t="s">
+        <v>291</v>
       </c>
       <c r="C39" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>328</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="H39" s="10">
+        <v>11812264</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O39" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P39" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="D39" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G39" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="H39" s="22">
-        <v>11812264</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="J39" s="6" t="s">
-        <v>337</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="L39" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="M39" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="N39" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="O39" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="P39" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="Q39" s="6" t="s">
-        <v>338</v>
+      <c r="Q39" s="4" t="s">
+        <v>332</v>
       </c>
       <c r="R39" s="7" t="s">
         <v>25</v>
       </c>
+      <c r="S39" s="7"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" ht="56" x14ac:dyDescent="0.3">
       <c r="A40" s="7">
         <v>39</v>
       </c>
+      <c r="B40" s="4" t="s">
+        <v>290</v>
+      </c>
       <c r="C40" s="7" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I40" s="7" t="s">
-        <v>345</v>
-      </c>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
       <c r="M40" s="7" t="s">
         <v>33</v>
       </c>
       <c r="N40" s="7" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="O40" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="P40" s="7" t="s">
-        <v>347</v>
+      <c r="P40" s="4" t="s">
+        <v>341</v>
       </c>
       <c r="Q40" s="7" t="s">
         <v>24</v>
       </c>
       <c r="R40" s="7" t="s">
         <v>25</v>
+      </c>
+      <c r="S40" s="7"/>
+    </row>
+    <row r="41" spans="1:19" ht="56" x14ac:dyDescent="0.3">
+      <c r="A41" s="7">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R41" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S41" s="7"/>
+    </row>
+    <row r="42" spans="1:19" ht="112" x14ac:dyDescent="0.3">
+      <c r="A42" s="7">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="H42" s="7">
+        <v>30135721</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="O42" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q42" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R42" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S42" s="7"/>
+    </row>
+    <row r="43" spans="1:19" ht="70" x14ac:dyDescent="0.3">
+      <c r="A43" s="7">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="H43" s="7">
+        <v>17202168</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="R43" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S43" s="7"/>
+    </row>
+    <row r="44" spans="1:19" ht="98" x14ac:dyDescent="0.3">
+      <c r="A44" s="7">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>365</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="H44" s="7">
+        <v>10592173</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="L44" s="7"/>
+      <c r="M44" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O44" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P44" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q44" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="R44" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S44" s="7">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" ht="168" x14ac:dyDescent="0.3">
+      <c r="A45" s="7">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="H45" s="5">
+        <v>39558185</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="K45" s="7"/>
+      <c r="L45" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="M45" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O45" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P45" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q45" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="R45" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="S45" s="7"/>
+    </row>
+    <row r="46" spans="1:19" ht="168" x14ac:dyDescent="0.3">
+      <c r="A46" s="3">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H46" s="5">
+        <v>34718710</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R46" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="3">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -4446,8 +4690,9 @@
     <hyperlink ref="E35" r:id="rId45" xr:uid="{944DD57D-6054-446C-8A3C-0023E5B9F84C}"/>
     <hyperlink ref="E37" r:id="rId46" xr:uid="{E243C969-D32B-42B8-8FEF-3E974F93FDE5}"/>
     <hyperlink ref="E36" r:id="rId47" xr:uid="{000FD2BC-18E2-48A1-887F-40CEA0556CBF}"/>
+    <hyperlink ref="G43" r:id="rId48" display="http://www.ncbi.nlm.nih.gov/pubmed/34986597" xr:uid="{B8644584-D844-4AE0-AA42-9BA4EB1D2DF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId48"/>
+  <pageSetup orientation="portrait" r:id="rId49"/>
 </worksheet>
 </file>
--- a/doc/POPPy.xlsx
+++ b/doc/POPPy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oreil\Documents\GitHub\poppy\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7A82CB6-F701-45EA-9588-880CDE1A8495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{690C877D-0D48-4DFD-B33B-89C247A205A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -929,9 +929,6 @@
   </si>
   <si>
     <t>Plant taxonomy- general</t>
-  </si>
-  <si>
-    <t>http://bidd2.nus.edu.sg/CMAUP/</t>
   </si>
   <si>
     <t>Journal Article</t>
@@ -1446,6 +1443,9 @@
   </si>
   <si>
     <t>van Santen JA, Poynton EF, Iskakova D, McMann E, Alsup TA, Clark TN, Fergusson CH, Fewer DP, Hughes AH, McCadden CA, Parra J, Soldatou S, Rudolf JD, Janssen EM, Duncan KR, Linington RG. The Natural Products Atlas 2.0: a database of microbially-derived natural products. Nucleic Acids Res. 2022 Jan 7;50(D1):D1317-D1323. doi: 10.1093/nar/gkab941. PMID: 34718710; PMCID: PMC8728154.</t>
+  </si>
+  <si>
+    <t>https://bidd.group/CMAUP/</t>
   </si>
 </sst>
 </file>
@@ -1566,7 +1566,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1612,6 +1612,10 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2320,7 +2324,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>293</v>
@@ -2335,7 +2339,7 @@
         <v>60</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>33</v>
@@ -2438,7 +2442,7 @@
         <v>33</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H8" s="10">
         <v>17989687</v>
@@ -2510,7 +2514,7 @@
         <v>88</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>33</v>
@@ -2534,7 +2538,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="238" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="238.5" x14ac:dyDescent="0.35">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -2547,7 +2551,7 @@
       <c r="D10" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="21" t="s">
         <v>91</v>
       </c>
       <c r="F10" s="8" t="s">
@@ -2593,7 +2597,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="154" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" ht="154.5" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -2606,11 +2610,11 @@
       <c r="D11" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="E11" s="9" t="s">
-        <v>296</v>
+      <c r="E11" s="22" t="s">
+        <v>387</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>101</v>
@@ -2787,7 +2791,7 @@
         <v>128</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>33</v>
@@ -2846,7 +2850,7 @@
         <v>136</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>33</v>
@@ -2935,7 +2939,7 @@
         <v>290</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>292</v>
@@ -3109,7 +3113,7 @@
         <v>175</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E20" s="14" t="s">
         <v>176</v>
@@ -3133,7 +3137,7 @@
         <v>179</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M20" s="7" t="s">
         <v>33</v>
@@ -3166,7 +3170,7 @@
         <v>181</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E21" s="14" t="s">
         <v>182</v>
@@ -3190,7 +3194,7 @@
         <v>185</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>33</v>
@@ -3225,7 +3229,7 @@
         <v>186</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>187</v>
@@ -3249,7 +3253,7 @@
         <v>190</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M22" s="7" t="s">
         <v>33</v>
@@ -3284,7 +3288,7 @@
         <v>192</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E23" s="14" t="s">
         <v>193</v>
@@ -3308,7 +3312,7 @@
         <v>196</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M23" s="7" t="s">
         <v>33</v>
@@ -3343,7 +3347,7 @@
         <v>198</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E24" s="14" t="s">
         <v>199</v>
@@ -3367,7 +3371,7 @@
         <v>202</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>33</v>
@@ -3400,7 +3404,7 @@
         <v>204</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E25" s="14" t="s">
         <v>205</v>
@@ -3409,7 +3413,7 @@
         <v>33</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>293</v>
@@ -3424,7 +3428,7 @@
         <v>202</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>33</v>
@@ -3800,13 +3804,13 @@
         <v>222</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>293</v>
@@ -3857,7 +3861,7 @@
         <v>222</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>33</v>
@@ -3914,7 +3918,7 @@
         <v>222</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>33</v>
@@ -3971,7 +3975,7 @@
         <v>292</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>33</v>
@@ -4030,28 +4034,28 @@
         <v>292</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>293</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="M36" s="7" t="s">
         <v>33</v>
@@ -4060,16 +4064,16 @@
         <v>33</v>
       </c>
       <c r="O36" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="P36" s="7" t="s">
         <v>246</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="S36" s="7">
         <v>2025</v>
@@ -4083,30 +4087,30 @@
         <v>294</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>293</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J37" s="17"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M37" s="7" t="s">
         <v>33</v>
@@ -4124,7 +4128,7 @@
         <v>33</v>
       </c>
       <c r="R37" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="S37" s="7"/>
     </row>
@@ -4136,42 +4140,42 @@
         <v>290</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D38" s="7" t="s">
         <v>292</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H38" s="10">
         <v>24285751</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L38" s="7"/>
       <c r="M38" s="7" t="s">
         <v>24</v>
       </c>
       <c r="N38" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="O38" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="O38" s="7" t="s">
-        <v>325</v>
-      </c>
       <c r="P38" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q38" s="7" t="s">
         <v>24</v>
@@ -4191,34 +4195,34 @@
         <v>291</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D39" s="7" t="s">
         <v>292</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F39" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H39" s="10">
         <v>11812264</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="M39" s="7" t="s">
         <v>33</v>
@@ -4230,10 +4234,10 @@
         <v>33</v>
       </c>
       <c r="P39" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="R39" s="7" t="s">
         <v>25</v>
@@ -4248,13 +4252,13 @@
         <v>290</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D40" s="7" t="s">
         <v>292</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>33</v>
@@ -4264,7 +4268,7 @@
         <v>293</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
@@ -4273,13 +4277,13 @@
         <v>33</v>
       </c>
       <c r="N40" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="O40" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P40" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="O40" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="Q40" s="7" t="s">
         <v>24</v>
@@ -4297,13 +4301,13 @@
         <v>290</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D41" s="7" t="s">
         <v>222</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>33</v>
@@ -4313,12 +4317,12 @@
         <v>293</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
       <c r="L41" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>33</v>
@@ -4330,7 +4334,7 @@
         <v>33</v>
       </c>
       <c r="P41" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q41" s="7" t="s">
         <v>24</v>
@@ -4348,46 +4352,46 @@
         <v>290</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D42" s="7" t="s">
         <v>292</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H42" s="7">
         <v>30135721</v>
       </c>
       <c r="I42" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="J42" s="4" t="s">
         <v>349</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>350</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>153</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="M42" s="7" t="s">
         <v>33</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O42" s="7" t="s">
         <v>33</v>
       </c>
       <c r="P42" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="Q42" s="7" t="s">
         <v>24</v>
@@ -4405,49 +4409,49 @@
         <v>291</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D43" s="7" t="s">
         <v>292</v>
       </c>
       <c r="E43" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="18" t="s">
         <v>354</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G43" s="18" t="s">
-        <v>355</v>
       </c>
       <c r="H43" s="7">
         <v>17202168</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>153</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="M43" s="7" t="s">
         <v>33</v>
       </c>
       <c r="N43" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="O43" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="P43" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="O43" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="P43" s="4" t="s">
+      <c r="Q43" s="7" t="s">
         <v>357</v>
-      </c>
-      <c r="Q43" s="7" t="s">
-        <v>358</v>
       </c>
       <c r="R43" s="7" t="s">
         <v>25</v>
@@ -4462,31 +4466,31 @@
         <v>291</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D44" s="7" t="s">
         <v>292</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H44" s="7">
         <v>10592173</v>
       </c>
       <c r="I44" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="K44" s="7" t="s">
         <v>362</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>363</v>
       </c>
       <c r="L44" s="7"/>
       <c r="M44" s="7" t="s">
@@ -4519,32 +4523,32 @@
         <v>290</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D45" s="7" t="s">
         <v>292</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F45" s="7" t="s">
         <v>33</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H45" s="5">
         <v>39558185</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="M45" s="7" t="s">
         <v>33</v>
@@ -4556,7 +4560,7 @@
         <v>33</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="Q45" s="7" t="s">
         <v>24</v>
@@ -4574,34 +4578,34 @@
         <v>291</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>292</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>33</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H46" s="5">
         <v>34718710</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="J46" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="L46" s="2" t="s">
         <v>383</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>384</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>33</v>
@@ -4613,7 +4617,7 @@
         <v>33</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>24</v>
@@ -4629,17 +4633,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Phytochemical- general">
-      <formula>NOT(ISERROR(SEARCH("Phytochemical- general",B1)))</formula>
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Plant taxonomy- general">
+      <formula>NOT(ISERROR(SEARCH("Plant taxonomy- general",B1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Plant taxonomy- medicinal">
+      <formula>NOT(ISERROR(SEARCH("Plant taxonomy- medicinal",B1)))</formula>
     </cfRule>
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Biomedical- general">
       <formula>NOT(ISERROR(SEARCH("Biomedical- general",B1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Plant taxonomy- medicinal">
-      <formula>NOT(ISERROR(SEARCH("Plant taxonomy- medicinal",B1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Plant taxonomy- general">
-      <formula>NOT(ISERROR(SEARCH("Plant taxonomy- general",B1)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Phytochemical- general">
+      <formula>NOT(ISERROR(SEARCH("Phytochemical- general",B1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
